--- a/outputs/019eba6d-2222-7532-a606-ae934df05248/Laboratory work_1_Togysbayev_Tamerlan.xlsx
+++ b/outputs/019eba6d-2222-7532-a606-ae934df05248/Laboratory work_1_Togysbayev_Tamerlan.xlsx
@@ -622,9 +622,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T706"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -646,7 +646,7 @@
     <col min="20" max="20" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" ht="31.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +708,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" ns3:dyDescent="0.2">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -774,7 +774,7 @@
         <v>2745</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" ns3:dyDescent="0.2">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -840,7 +840,7 @@
         <v>39400</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" ns3:dyDescent="0.2">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -906,7 +906,7 @@
         <v>137430</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" ns3:dyDescent="0.2">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -972,7 +972,7 @@
         <v>1237.5</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" ns3:dyDescent="0.2">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>117406</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" ns3:dyDescent="0.2">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>17662.32</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" ns3:dyDescent="0.2">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>142861.5</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" ns3:dyDescent="0.2">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>3150.3999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" ns3:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>6771.2000000000007</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" ns3:dyDescent="0.2">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>24343.199999999997</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" ns3:dyDescent="0.2">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>26524</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" ns3:dyDescent="0.2">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -1500,7 +1500,7 @@
         <v>3875.8500000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" ns3:dyDescent="0.2">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -1566,7 +1566,7 @@
         <v>52200</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" ns3:dyDescent="0.2">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>15772.400000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" ns3:dyDescent="0.2">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>1556.8100000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" ns3:dyDescent="0.2">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>18074.400000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20" ns3:dyDescent="0.2">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>11577.449999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" ns3:dyDescent="0.2">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>32567</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20" ns3:dyDescent="0.2">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>-3727.5</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" ns3:dyDescent="0.2">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>33358</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" ns3:dyDescent="0.2">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>3468.9599999999991</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" ns3:dyDescent="0.2">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>7406</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" ns3:dyDescent="0.2">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>17693.28</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" ns3:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>7718.4</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" ns3:dyDescent="0.2">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>21879</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" ns3:dyDescent="0.2">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>2194.25</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:20" ns3:dyDescent="0.2">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -2490,7 +2490,7 @@
         <v>-8286.25</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:20" ns3:dyDescent="0.2">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -2556,7 +2556,7 @@
         <v>467.40000000000009</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:20" ns3:dyDescent="0.2">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -2622,7 +2622,7 @@
         <v>-24160</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:20" ns3:dyDescent="0.2">
       <c r="A31" t="s">
         <v>28</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>29904</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:20" ns3:dyDescent="0.2">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>20873.16</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:20" ns3:dyDescent="0.2">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -2820,7 +2820,7 @@
         <v>3270.8</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:20" ns3:dyDescent="0.2">
       <c r="A34" t="s">
         <v>20</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:20" ns3:dyDescent="0.2">
       <c r="A35" t="s">
         <v>30</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>-12787.5</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:20" ns3:dyDescent="0.2">
       <c r="A36" t="s">
         <v>20</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>7163</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:20" ns3:dyDescent="0.2">
       <c r="A37" t="s">
         <v>30</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:20" ns3:dyDescent="0.2">
       <c r="A38" t="s">
         <v>30</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:20" ns3:dyDescent="0.2">
       <c r="A39" t="s">
         <v>35</v>
       </c>
@@ -3216,7 +3216,7 @@
         <v>6802.08</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:20" ns3:dyDescent="0.2">
       <c r="A40" t="s">
         <v>26</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>23218</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:20" ns3:dyDescent="0.2">
       <c r="A41" t="s">
         <v>30</v>
       </c>
@@ -3348,7 +3348,7 @@
         <v>2486.25</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:20" ns3:dyDescent="0.2">
       <c r="A42" t="s">
         <v>35</v>
       </c>
@@ -3414,7 +3414,7 @@
         <v>6802.08</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:20" ns3:dyDescent="0.2">
       <c r="A43" t="s">
         <v>30</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>2486.25</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:20" ns3:dyDescent="0.2">
       <c r="A44" t="s">
         <v>26</v>
       </c>
@@ -3546,7 +3546,7 @@
         <v>23218</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:20" ns3:dyDescent="0.2">
       <c r="A45" t="s">
         <v>26</v>
       </c>
@@ -3612,7 +3612,7 @@
         <v>9416</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:20" ns3:dyDescent="0.2">
       <c r="A46" t="s">
         <v>30</v>
       </c>
@@ -3678,7 +3678,7 @@
         <v>2022.5</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:20" ns3:dyDescent="0.2">
       <c r="A47" t="s">
         <v>30</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>5362.5</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:20" ns3:dyDescent="0.2">
       <c r="A48" t="s">
         <v>28</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>246178</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:20" ns3:dyDescent="0.2">
       <c r="A49" t="s">
         <v>30</v>
       </c>
@@ -3876,7 +3876,7 @@
         <v>2022.5</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:20" ns3:dyDescent="0.2">
       <c r="A50" t="s">
         <v>30</v>
       </c>
@@ -3942,7 +3942,7 @@
         <v>5362.5</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:20" ns3:dyDescent="0.2">
       <c r="A51" t="s">
         <v>26</v>
       </c>
@@ -4008,7 +4008,7 @@
         <v>9416</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:20" ns3:dyDescent="0.2">
       <c r="A52" t="s">
         <v>28</v>
       </c>
@@ -4074,7 +4074,7 @@
         <v>246178</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:20" ns3:dyDescent="0.2">
       <c r="A53" t="s">
         <v>20</v>
       </c>
@@ -4140,7 +4140,7 @@
         <v>8849.75</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:20" ns3:dyDescent="0.2">
       <c r="A54" t="s">
         <v>20</v>
       </c>
@@ -4206,7 +4206,7 @@
         <v>8849.75</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:20" ns3:dyDescent="0.2">
       <c r="A55" t="s">
         <v>28</v>
       </c>
@@ -4272,7 +4272,7 @@
         <v>4903.7200000000012</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:20" ns3:dyDescent="0.2">
       <c r="A56" t="s">
         <v>28</v>
       </c>
@@ -4338,7 +4338,7 @@
         <v>4903.7200000000012</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:20" ns3:dyDescent="0.2">
       <c r="A57" t="s">
         <v>20</v>
       </c>
@@ -4404,7 +4404,7 @@
         <v>2952.3999999999996</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:20" ns3:dyDescent="0.2">
       <c r="A58" t="s">
         <v>20</v>
       </c>
@@ -4470,7 +4470,7 @@
         <v>6661.5999999999985</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:20" ns3:dyDescent="0.2">
       <c r="A59" t="s">
         <v>20</v>
       </c>
@@ -4536,7 +4536,7 @@
         <v>6661.5999999999985</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:20" ns3:dyDescent="0.2">
       <c r="A60" t="s">
         <v>20</v>
       </c>
@@ -4602,7 +4602,7 @@
         <v>2952.3999999999996</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:20" ns3:dyDescent="0.2">
       <c r="A61" t="s">
         <v>28</v>
       </c>
@@ -4668,7 +4668,7 @@
         <v>1912.3500000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:20" ns3:dyDescent="0.2">
       <c r="A62" t="s">
         <v>28</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>1912.3500000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:20" ns3:dyDescent="0.2">
       <c r="A63" t="s">
         <v>28</v>
       </c>
@@ -4800,7 +4800,7 @@
         <v>89030</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:20" ns3:dyDescent="0.2">
       <c r="A64" t="s">
         <v>28</v>
       </c>
@@ -4866,7 +4866,7 @@
         <v>12501</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:20" ns3:dyDescent="0.2">
       <c r="A65" t="s">
         <v>30</v>
       </c>
@@ -4932,7 +4932,7 @@
         <v>-880</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:20" ns3:dyDescent="0.2">
       <c r="A66" t="s">
         <v>30</v>
       </c>
@@ -4998,7 +4998,7 @@
         <v>-880</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:20" ns3:dyDescent="0.2">
       <c r="A67" t="s">
         <v>28</v>
       </c>
@@ -5064,7 +5064,7 @@
         <v>12501</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:20" ns3:dyDescent="0.2">
       <c r="A68" t="s">
         <v>28</v>
       </c>
@@ -5130,7 +5130,7 @@
         <v>89030</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:20" ns3:dyDescent="0.2">
       <c r="A69" t="s">
         <v>35</v>
       </c>
@@ -5196,7 +5196,7 @@
         <v>19035.72</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:20" ns3:dyDescent="0.2">
       <c r="A70" t="s">
         <v>28</v>
       </c>
@@ -5262,7 +5262,7 @@
         <v>2216.7399999999998</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:20" ns3:dyDescent="0.2">
       <c r="A71" t="s">
         <v>35</v>
       </c>
@@ -5328,7 +5328,7 @@
         <v>19035.72</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:20" ns3:dyDescent="0.2">
       <c r="A72" t="s">
         <v>28</v>
       </c>
@@ -5394,7 +5394,7 @@
         <v>50163</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:20" ns3:dyDescent="0.2">
       <c r="A73" t="s">
         <v>26</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>39072</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:20" ns3:dyDescent="0.2">
       <c r="A74" t="s">
         <v>28</v>
       </c>
@@ -5526,7 +5526,7 @@
         <v>143244</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:20" ns3:dyDescent="0.2">
       <c r="A75" t="s">
         <v>26</v>
       </c>
@@ -5592,7 +5592,7 @@
         <v>39072</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:20" ns3:dyDescent="0.2">
       <c r="A76" t="s">
         <v>28</v>
       </c>
@@ -5658,7 +5658,7 @@
         <v>50163</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:20" ns3:dyDescent="0.2">
       <c r="A77" t="s">
         <v>28</v>
       </c>
@@ -5724,7 +5724,7 @@
         <v>2216.7399999999998</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:20" ns3:dyDescent="0.2">
       <c r="A78" t="s">
         <v>28</v>
       </c>
@@ -5790,7 +5790,7 @@
         <v>143244</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:20" ns3:dyDescent="0.2">
       <c r="A79" t="s">
         <v>28</v>
       </c>
@@ -5856,7 +5856,7 @@
         <v>15461.599999999999</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:20" ns3:dyDescent="0.2">
       <c r="A80" t="s">
         <v>28</v>
       </c>
@@ -5922,7 +5922,7 @@
         <v>15461.599999999999</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:20" ns3:dyDescent="0.2">
       <c r="A81" t="s">
         <v>35</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>2906.64</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:20" ns3:dyDescent="0.2">
       <c r="A82" t="s">
         <v>35</v>
       </c>
@@ -6054,7 +6054,7 @@
         <v>2906.64</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:20" ns3:dyDescent="0.2">
       <c r="A83" t="s">
         <v>35</v>
       </c>
@@ -6120,7 +6120,7 @@
         <v>3010.8</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:20" ns3:dyDescent="0.2">
       <c r="A84" t="s">
         <v>35</v>
       </c>
@@ -6186,7 +6186,7 @@
         <v>3010.8</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:20" ns3:dyDescent="0.2">
       <c r="A85" t="s">
         <v>20</v>
       </c>
@@ -6252,7 +6252,7 @@
         <v>7584.5</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:20" ns3:dyDescent="0.2">
       <c r="A86" t="s">
         <v>26</v>
       </c>
@@ -6318,7 +6318,7 @@
         <v>45880</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:20" ns3:dyDescent="0.2">
       <c r="A87" t="s">
         <v>26</v>
       </c>
@@ -6384,7 +6384,7 @@
         <v>45880</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:20" ns3:dyDescent="0.2">
       <c r="A88" t="s">
         <v>20</v>
       </c>
@@ -6450,7 +6450,7 @@
         <v>7584.5</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:20" ns3:dyDescent="0.2">
       <c r="A89" t="s">
         <v>35</v>
       </c>
@@ -6516,7 +6516,7 @@
         <v>9200.64</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:20" ns3:dyDescent="0.2">
       <c r="A90" t="s">
         <v>35</v>
       </c>
@@ -6582,7 +6582,7 @@
         <v>9200.64</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:20" ns3:dyDescent="0.2">
       <c r="A91" t="s">
         <v>28</v>
       </c>
@@ -6648,7 +6648,7 @@
         <v>23337.599999999999</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:20" ns3:dyDescent="0.2">
       <c r="A92" t="s">
         <v>28</v>
       </c>
@@ -6714,7 +6714,7 @@
         <v>23337.599999999999</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:20" ns3:dyDescent="0.2">
       <c r="A93" t="s">
         <v>28</v>
       </c>
@@ -6780,7 +6780,7 @@
         <v>17716</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:20" ns3:dyDescent="0.2">
       <c r="A94" t="s">
         <v>28</v>
       </c>
@@ -6846,7 +6846,7 @@
         <v>17716</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:20" ns3:dyDescent="0.2">
       <c r="A95" t="s">
         <v>28</v>
       </c>
@@ -6912,7 +6912,7 @@
         <v>13034</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:20" ns3:dyDescent="0.2">
       <c r="A96" t="s">
         <v>28</v>
       </c>
@@ -6978,7 +6978,7 @@
         <v>13034</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:20" ns3:dyDescent="0.2">
       <c r="A97" t="s">
         <v>28</v>
       </c>
@@ -7044,7 +7044,7 @@
         <v>3055.9199999999983</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:20" ns3:dyDescent="0.2">
       <c r="A98" t="s">
         <v>28</v>
       </c>
@@ -7110,7 +7110,7 @@
         <v>3055.9199999999983</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:20" ns3:dyDescent="0.2">
       <c r="A99" t="s">
         <v>28</v>
       </c>
@@ -7176,7 +7176,7 @@
         <v>1761.5400000000009</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:20" ns3:dyDescent="0.2">
       <c r="A100" t="s">
         <v>20</v>
       </c>
@@ -7242,7 +7242,7 @@
         <v>5054.7000000000007</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:20" ns3:dyDescent="0.2">
       <c r="A101" t="s">
         <v>26</v>
       </c>
@@ -7308,7 +7308,7 @@
         <v>2152</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:20" ns3:dyDescent="0.2">
       <c r="A102" t="s">
         <v>26</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>2152</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:20" ns3:dyDescent="0.2">
       <c r="A103" t="s">
         <v>20</v>
       </c>
@@ -7440,7 +7440,7 @@
         <v>5054.7000000000007</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:20" ns3:dyDescent="0.2">
       <c r="A104" t="s">
         <v>28</v>
       </c>
@@ -7506,7 +7506,7 @@
         <v>1761.5400000000009</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:20" ns3:dyDescent="0.2">
       <c r="A105" t="s">
         <v>28</v>
       </c>
@@ -7572,7 +7572,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:20" ns3:dyDescent="0.2">
       <c r="A106" t="s">
         <v>28</v>
       </c>
@@ -7638,7 +7638,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:20" ns3:dyDescent="0.2">
       <c r="A107" t="s">
         <v>28</v>
       </c>
@@ -7704,7 +7704,7 @@
         <v>155250</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:20" ns3:dyDescent="0.2">
       <c r="A108" t="s">
         <v>35</v>
       </c>
@@ -7770,7 +7770,7 @@
         <v>8208</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:20" ns3:dyDescent="0.2">
       <c r="A109" t="s">
         <v>28</v>
       </c>
@@ -7836,7 +7836,7 @@
         <v>4037.5599999999995</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:20" ns3:dyDescent="0.2">
       <c r="A110" t="s">
         <v>20</v>
       </c>
@@ -7902,7 +7902,7 @@
         <v>1556.8500000000004</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:20" ns3:dyDescent="0.2">
       <c r="A111" t="s">
         <v>28</v>
       </c>
@@ -7968,7 +7968,7 @@
         <v>3989.7000000000007</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:20" ns3:dyDescent="0.2">
       <c r="A112" t="s">
         <v>30</v>
       </c>
@@ -8034,7 +8034,7 @@
         <v>4150</v>
       </c>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:20" ns3:dyDescent="0.2">
       <c r="A113" t="s">
         <v>35</v>
       </c>
@@ -8100,7 +8100,7 @@
         <v>15636.599999999999</v>
       </c>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:20" ns3:dyDescent="0.2">
       <c r="A114" t="s">
         <v>28</v>
       </c>
@@ -8166,7 +8166,7 @@
         <v>1676.3999999999996</v>
       </c>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:20" ns3:dyDescent="0.2">
       <c r="A115" t="s">
         <v>28</v>
       </c>
@@ -8232,7 +8232,7 @@
         <v>11385</v>
       </c>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:20" ns3:dyDescent="0.2">
       <c r="A116" t="s">
         <v>28</v>
       </c>
@@ -8298,7 +8298,7 @@
         <v>20673</v>
       </c>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:20" ns3:dyDescent="0.2">
       <c r="A117" t="s">
         <v>28</v>
       </c>
@@ -8364,7 +8364,7 @@
         <v>415.53999999999996</v>
       </c>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:20" ns3:dyDescent="0.2">
       <c r="A118" t="s">
         <v>28</v>
       </c>
@@ -8430,7 +8430,7 @@
         <v>9882.4000000000015</v>
       </c>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:20" ns3:dyDescent="0.2">
       <c r="A119" t="s">
         <v>30</v>
       </c>
@@ -8496,7 +8496,7 @@
         <v>-9375</v>
       </c>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:20" ns3:dyDescent="0.2">
       <c r="A120" t="s">
         <v>26</v>
       </c>
@@ -8562,7 +8562,7 @@
         <v>40716</v>
       </c>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:20" ns3:dyDescent="0.2">
       <c r="A121" t="s">
         <v>35</v>
       </c>
@@ -8628,7 +8628,7 @@
         <v>22546.080000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:20" ns3:dyDescent="0.2">
       <c r="A122" t="s">
         <v>28</v>
       </c>
@@ -8694,7 +8694,7 @@
         <v>133052</v>
       </c>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:20" ns3:dyDescent="0.2">
       <c r="A123" t="s">
         <v>26</v>
       </c>
@@ -8760,7 +8760,7 @@
         <v>10036</v>
       </c>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:20" ns3:dyDescent="0.2">
       <c r="A124" t="s">
         <v>30</v>
       </c>
@@ -8826,7 +8826,7 @@
         <v>-11606.25</v>
       </c>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:20" ns3:dyDescent="0.2">
       <c r="A125" t="s">
         <v>35</v>
       </c>
@@ -8892,7 +8892,7 @@
         <v>14058</v>
       </c>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:20" ns3:dyDescent="0.2">
       <c r="A126" t="s">
         <v>20</v>
       </c>
@@ -8958,7 +8958,7 @@
         <v>3540.5</v>
       </c>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:20" ns3:dyDescent="0.2">
       <c r="A127" t="s">
         <v>28</v>
       </c>
@@ -9024,7 +9024,7 @@
         <v>21992.400000000001</v>
       </c>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:20" ns3:dyDescent="0.2">
       <c r="A128" t="s">
         <v>30</v>
       </c>
@@ -9090,7 +9090,7 @@
         <v>-13530</v>
       </c>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:20" ns3:dyDescent="0.2">
       <c r="A129" t="s">
         <v>20</v>
       </c>
@@ -9156,7 +9156,7 @@
         <v>5226</v>
       </c>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:20" ns3:dyDescent="0.2">
       <c r="A130" t="s">
         <v>28</v>
       </c>
@@ -9222,7 +9222,7 @@
         <v>3328.380000000001</v>
       </c>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:20" ns3:dyDescent="0.2">
       <c r="A131" t="s">
         <v>28</v>
       </c>
@@ -9288,7 +9288,7 @@
         <v>22893</v>
       </c>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:20" ns3:dyDescent="0.2">
       <c r="A132" t="s">
         <v>20</v>
       </c>
@@ -9354,7 +9354,7 @@
         <v>8153.5999999999985</v>
       </c>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:20" ns3:dyDescent="0.2">
       <c r="A133" t="s">
         <v>26</v>
       </c>
@@ -9420,7 +9420,7 @@
         <v>28655</v>
       </c>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:20" ns3:dyDescent="0.2">
       <c r="A134" t="s">
         <v>35</v>
       </c>
@@ -9486,7 +9486,7 @@
         <v>16265.04</v>
       </c>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:20" ns3:dyDescent="0.2">
       <c r="A135" t="s">
         <v>28</v>
       </c>
@@ -9552,7 +9552,7 @@
         <v>78802</v>
       </c>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:20" ns3:dyDescent="0.2">
       <c r="A136" t="s">
         <v>26</v>
       </c>
@@ -9618,7 +9618,7 @@
         <v>20288</v>
       </c>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:20" ns3:dyDescent="0.2">
       <c r="A137" t="s">
         <v>20</v>
       </c>
@@ -9684,7 +9684,7 @@
         <v>5423</v>
       </c>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:20" ns3:dyDescent="0.2">
       <c r="A138" t="s">
         <v>28</v>
       </c>
@@ -9750,7 +9750,7 @@
         <v>75262.5</v>
       </c>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:20" ns3:dyDescent="0.2">
       <c r="A139" t="s">
         <v>28</v>
       </c>
@@ -9816,7 +9816,7 @@
         <v>80662.5</v>
       </c>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:20" ns3:dyDescent="0.2">
       <c r="A140" t="s">
         <v>26</v>
       </c>
@@ -9882,7 +9882,7 @@
         <v>12870</v>
       </c>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:20" ns3:dyDescent="0.2">
       <c r="A141" t="s">
         <v>30</v>
       </c>
@@ -9948,7 +9948,7 @@
         <v>-40617.5</v>
       </c>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:20" ns3:dyDescent="0.2">
       <c r="A142" t="s">
         <v>20</v>
       </c>
@@ -10014,7 +10014,7 @@
         <v>10760</v>
       </c>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:20" ns3:dyDescent="0.2">
       <c r="A143" t="s">
         <v>20</v>
       </c>
@@ -10080,7 +10080,7 @@
         <v>9047.5</v>
       </c>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:20" ns3:dyDescent="0.2">
       <c r="A144" t="s">
         <v>28</v>
       </c>
@@ -10146,7 +10146,7 @@
         <v>3744.1800000000003</v>
       </c>
     </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:20" ns3:dyDescent="0.2">
       <c r="A145" t="s">
         <v>28</v>
       </c>
@@ -10212,7 +10212,7 @@
         <v>5222.3999999999996</v>
       </c>
     </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:20" ns3:dyDescent="0.2">
       <c r="A146" t="s">
         <v>28</v>
       </c>
@@ -10278,7 +10278,7 @@
         <v>22078</v>
       </c>
     </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:20" ns3:dyDescent="0.2">
       <c r="A147" t="s">
         <v>28</v>
       </c>
@@ -10344,7 +10344,7 @@
         <v>161020</v>
       </c>
     </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:20" ns3:dyDescent="0.2">
       <c r="A148" t="s">
         <v>35</v>
       </c>
@@ -10410,7 +10410,7 @@
         <v>7845.1200000000008</v>
       </c>
     </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:20" ns3:dyDescent="0.2">
       <c r="A149" t="s">
         <v>20</v>
       </c>
@@ -10476,7 +10476,7 @@
         <v>9948.4000000000015</v>
       </c>
     </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:20" ns3:dyDescent="0.2">
       <c r="A150" t="s">
         <v>28</v>
       </c>
@@ -10542,7 +10542,7 @@
         <v>135128</v>
       </c>
     </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:20" ns3:dyDescent="0.2">
       <c r="A151" t="s">
         <v>26</v>
       </c>
@@ -10608,7 +10608,7 @@
         <v>38500</v>
       </c>
     </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:20" ns3:dyDescent="0.2">
       <c r="A152" t="s">
         <v>28</v>
       </c>
@@ -10674,7 +10674,7 @@
         <v>16218</v>
       </c>
     </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:20" ns3:dyDescent="0.2">
       <c r="A153" t="s">
         <v>28</v>
       </c>
@@ -10740,7 +10740,7 @@
         <v>3524.3999999999996</v>
       </c>
     </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:20" ns3:dyDescent="0.2">
       <c r="A154" t="s">
         <v>20</v>
       </c>
@@ -10806,7 +10806,7 @@
         <v>8993</v>
       </c>
     </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:20" ns3:dyDescent="0.2">
       <c r="A155" t="s">
         <v>28</v>
       </c>
@@ -10872,7 +10872,7 @@
         <v>9297</v>
       </c>
     </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:20" ns3:dyDescent="0.2">
       <c r="A156" t="s">
         <v>30</v>
       </c>
@@ -10938,7 +10938,7 @@
         <v>-2217.5</v>
       </c>
     </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:20" ns3:dyDescent="0.2">
       <c r="A157" t="s">
         <v>26</v>
       </c>
@@ -11004,7 +11004,7 @@
         <v>77952</v>
       </c>
     </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:20" ns3:dyDescent="0.2">
       <c r="A158" t="s">
         <v>28</v>
       </c>
@@ -11070,7 +11070,7 @@
         <v>3208.75</v>
       </c>
     </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:20" ns3:dyDescent="0.2">
       <c r="A159" t="s">
         <v>28</v>
       </c>
@@ -11136,7 +11136,7 @@
         <v>12220.599999999999</v>
       </c>
     </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:20" ns3:dyDescent="0.2">
       <c r="A160" t="s">
         <v>28</v>
       </c>
@@ -11202,7 +11202,7 @@
         <v>5056.7999999999993</v>
       </c>
     </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:20" ns3:dyDescent="0.2">
       <c r="A161" t="s">
         <v>28</v>
       </c>
@@ -11268,7 +11268,7 @@
         <v>2802.24</v>
       </c>
     </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:20" ns3:dyDescent="0.2">
       <c r="A162" t="s">
         <v>26</v>
       </c>
@@ -11334,7 +11334,7 @@
         <v>21008</v>
       </c>
     </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:20" ns3:dyDescent="0.2">
       <c r="A163" t="s">
         <v>35</v>
       </c>
@@ -11400,7 +11400,7 @@
         <v>11055</v>
       </c>
     </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:20" ns3:dyDescent="0.2">
       <c r="A164" t="s">
         <v>28</v>
       </c>
@@ -11466,7 +11466,7 @@
         <v>2207.0699999999997</v>
       </c>
     </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:20" ns3:dyDescent="0.2">
       <c r="A165" t="s">
         <v>26</v>
       </c>
@@ -11532,7 +11532,7 @@
         <v>7682</v>
       </c>
     </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:20" ns3:dyDescent="0.2">
       <c r="A166" t="s">
         <v>35</v>
       </c>
@@ -11598,7 +11598,7 @@
         <v>2423.52</v>
       </c>
     </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:20" ns3:dyDescent="0.2">
       <c r="A167" t="s">
         <v>30</v>
       </c>
@@ -11664,7 +11664,7 @@
         <v>-11115</v>
       </c>
     </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:20" ns3:dyDescent="0.2">
       <c r="A168" t="s">
         <v>30</v>
       </c>
@@ -11730,7 +11730,7 @@
         <v>-14370</v>
       </c>
     </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:20" ns3:dyDescent="0.2">
       <c r="A169" t="s">
         <v>28</v>
       </c>
@@ -11796,7 +11796,7 @@
         <v>102850</v>
       </c>
     </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:20" ns3:dyDescent="0.2">
       <c r="A170" t="s">
         <v>26</v>
       </c>
@@ -11862,7 +11862,7 @@
         <v>16604</v>
       </c>
     </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:20" ns3:dyDescent="0.2">
       <c r="A171" t="s">
         <v>20</v>
       </c>
@@ -11928,7 +11928,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:20" ns3:dyDescent="0.2">
       <c r="A172" t="s">
         <v>35</v>
       </c>
@@ -11994,7 +11994,7 @@
         <v>13168.8</v>
       </c>
     </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:20" ns3:dyDescent="0.2">
       <c r="A173" t="s">
         <v>35</v>
       </c>
@@ -12060,7 +12060,7 @@
         <v>14749.8</v>
       </c>
     </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:20" ns3:dyDescent="0.2">
       <c r="A174" t="s">
         <v>30</v>
       </c>
@@ -12126,7 +12126,7 @@
         <v>-35262.5</v>
       </c>
     </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:20" ns3:dyDescent="0.2">
       <c r="A175" t="s">
         <v>28</v>
       </c>
@@ -12192,7 +12192,7 @@
         <v>52521</v>
       </c>
     </row>
-    <row r="176" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:20" ns3:dyDescent="0.2">
       <c r="A176" t="s">
         <v>30</v>
       </c>
@@ -12258,7 +12258,7 @@
         <v>-33522.5</v>
       </c>
     </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:20" ns3:dyDescent="0.2">
       <c r="A177" t="s">
         <v>28</v>
       </c>
@@ -12324,7 +12324,7 @@
         <v>16185</v>
       </c>
     </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:20" ns3:dyDescent="0.2">
       <c r="A178" t="s">
         <v>28</v>
       </c>
@@ -12390,7 +12390,7 @@
         <v>13210</v>
       </c>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:20" ns3:dyDescent="0.2">
       <c r="A179" t="s">
         <v>28</v>
       </c>
@@ -12456,7 +12456,7 @@
         <v>2986</v>
       </c>
     </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:20" ns3:dyDescent="0.2">
       <c r="A180" t="s">
         <v>28</v>
       </c>
@@ -12522,7 +12522,7 @@
         <v>7613.8499999999985</v>
       </c>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:20" ns3:dyDescent="0.2">
       <c r="A181" t="s">
         <v>26</v>
       </c>
@@ -12588,7 +12588,7 @@
         <v>99814.5</v>
       </c>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:20" ns3:dyDescent="0.2">
       <c r="A182" t="s">
         <v>35</v>
       </c>
@@ -12654,7 +12654,7 @@
         <v>21418.560000000001</v>
       </c>
     </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:20" ns3:dyDescent="0.2">
       <c r="A183" t="s">
         <v>28</v>
       </c>
@@ -12720,7 +12720,7 @@
         <v>7311.7200000000012</v>
       </c>
     </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:20" ns3:dyDescent="0.2">
       <c r="A184" t="s">
         <v>28</v>
       </c>
@@ -12786,7 +12786,7 @@
         <v>2263.7999999999993</v>
       </c>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:20" ns3:dyDescent="0.2">
       <c r="A185" t="s">
         <v>28</v>
       </c>
@@ -12852,7 +12852,7 @@
         <v>100376.25</v>
       </c>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:20" ns3:dyDescent="0.2">
       <c r="A186" t="s">
         <v>20</v>
       </c>
@@ -12918,7 +12918,7 @@
         <v>2358.75</v>
       </c>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:20" ns3:dyDescent="0.2">
       <c r="A187" t="s">
         <v>20</v>
       </c>
@@ -12984,7 +12984,7 @@
         <v>12159.25</v>
       </c>
     </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:20" ns3:dyDescent="0.2">
       <c r="A188" t="s">
         <v>28</v>
       </c>
@@ -13050,7 +13050,7 @@
         <v>9834</v>
       </c>
     </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:20" ns3:dyDescent="0.2">
       <c r="A189" t="s">
         <v>30</v>
       </c>
@@ -13116,7 +13116,7 @@
         <v>-4968.75</v>
       </c>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:20" ns3:dyDescent="0.2">
       <c r="A190" t="s">
         <v>35</v>
       </c>
@@ -13182,7 +13182,7 @@
         <v>19094.400000000001</v>
       </c>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:20" ns3:dyDescent="0.2">
       <c r="A191" t="s">
         <v>35</v>
       </c>
@@ -13248,7 +13248,7 @@
         <v>26475.120000000003</v>
       </c>
     </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:20" ns3:dyDescent="0.2">
       <c r="A192" t="s">
         <v>26</v>
       </c>
@@ -13314,7 +13314,7 @@
         <v>58995</v>
       </c>
     </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:20" ns3:dyDescent="0.2">
       <c r="A193" t="s">
         <v>28</v>
       </c>
@@ -13380,7 +13380,7 @@
         <v>141394.5</v>
       </c>
     </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:20" ns3:dyDescent="0.2">
       <c r="A194" t="s">
         <v>35</v>
       </c>
@@ -13446,7 +13446,7 @@
         <v>15491.52</v>
       </c>
     </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:20" ns3:dyDescent="0.2">
       <c r="A195" t="s">
         <v>20</v>
       </c>
@@ -13512,7 +13512,7 @@
         <v>2383.5</v>
       </c>
     </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:20" ns3:dyDescent="0.2">
       <c r="A196" t="s">
         <v>30</v>
       </c>
@@ -13578,7 +13578,7 @@
         <v>-4342.5</v>
       </c>
     </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:20" ns3:dyDescent="0.2">
       <c r="A197" t="s">
         <v>20</v>
       </c>
@@ -13644,7 +13644,7 @@
         <v>1286.3999999999996</v>
       </c>
     </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:20" ns3:dyDescent="0.2">
       <c r="A198" t="s">
         <v>28</v>
       </c>
@@ -13710,7 +13710,7 @@
         <v>39449</v>
       </c>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:20" ns3:dyDescent="0.2">
       <c r="A199" t="s">
         <v>26</v>
       </c>
@@ -13776,7 +13776,7 @@
         <v>14841</v>
       </c>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:20" ns3:dyDescent="0.2">
       <c r="A200" t="s">
         <v>35</v>
       </c>
@@ -13842,7 +13842,7 @@
         <v>13317.119999999999</v>
       </c>
     </row>
-    <row r="201" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:20" ns3:dyDescent="0.2">
       <c r="A201" t="s">
         <v>30</v>
       </c>
@@ -13908,7 +13908,7 @@
         <v>-4847.5</v>
       </c>
     </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:20" ns3:dyDescent="0.2">
       <c r="A202" t="s">
         <v>30</v>
       </c>
@@ -13974,7 +13974,7 @@
         <v>-27693.75</v>
       </c>
     </row>
-    <row r="203" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:20" ns3:dyDescent="0.2">
       <c r="A203" t="s">
         <v>28</v>
       </c>
@@ -14040,7 +14040,7 @@
         <v>20506.199999999997</v>
       </c>
     </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:20" ns3:dyDescent="0.2">
       <c r="A204" t="s">
         <v>26</v>
       </c>
@@ -14106,7 +14106,7 @@
         <v>48930</v>
       </c>
     </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:20" ns3:dyDescent="0.2">
       <c r="A205" t="s">
         <v>28</v>
       </c>
@@ -14172,7 +14172,7 @@
         <v>19163.400000000001</v>
       </c>
     </row>
-    <row r="206" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:20" ns3:dyDescent="0.2">
       <c r="A206" t="s">
         <v>28</v>
       </c>
@@ -14238,7 +14238,7 @@
         <v>43721.25</v>
       </c>
     </row>
-    <row r="207" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:20" ns3:dyDescent="0.2">
       <c r="A207" t="s">
         <v>28</v>
       </c>
@@ -14304,7 +14304,7 @@
         <v>1567.9650000000001</v>
       </c>
     </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:20" ns3:dyDescent="0.2">
       <c r="A208" t="s">
         <v>26</v>
       </c>
@@ -14370,7 +14370,7 @@
         <v>8877</v>
       </c>
     </row>
-    <row r="209" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:20" ns3:dyDescent="0.2">
       <c r="A209" t="s">
         <v>20</v>
       </c>
@@ -14436,7 +14436,7 @@
         <v>12192.375</v>
       </c>
     </row>
-    <row r="210" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:20" ns3:dyDescent="0.2">
       <c r="A210" t="s">
         <v>30</v>
       </c>
@@ -14502,7 +14502,7 @@
         <v>-18663.75</v>
       </c>
     </row>
-    <row r="211" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:20" ns3:dyDescent="0.2">
       <c r="A211" t="s">
         <v>28</v>
       </c>
@@ -14568,7 +14568,7 @@
         <v>91327.5</v>
       </c>
     </row>
-    <row r="212" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:20" ns3:dyDescent="0.2">
       <c r="A212" t="s">
         <v>28</v>
       </c>
@@ -14634,7 +14634,7 @@
         <v>2920</v>
       </c>
     </row>
-    <row r="213" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:20" ns3:dyDescent="0.2">
       <c r="A213" t="s">
         <v>20</v>
       </c>
@@ -14700,7 +14700,7 @@
         <v>4870</v>
       </c>
     </row>
-    <row r="214" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:20" ns3:dyDescent="0.2">
       <c r="A214" t="s">
         <v>30</v>
       </c>
@@ -14766,7 +14766,7 @@
         <v>9020</v>
       </c>
     </row>
-    <row r="215" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:20" ns3:dyDescent="0.2">
       <c r="A215" t="s">
         <v>26</v>
       </c>
@@ -14832,7 +14832,7 @@
         <v>100050</v>
       </c>
     </row>
-    <row r="216" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:20" ns3:dyDescent="0.2">
       <c r="A216" t="s">
         <v>28</v>
       </c>
@@ -14898,7 +14898,7 @@
         <v>247500</v>
       </c>
     </row>
-    <row r="217" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:20" ns3:dyDescent="0.2">
       <c r="A217" t="s">
         <v>20</v>
       </c>
@@ -14964,7 +14964,7 @@
         <v>11135.599999999999</v>
       </c>
     </row>
-    <row r="218" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:20" ns3:dyDescent="0.2">
       <c r="A218" t="s">
         <v>35</v>
       </c>
@@ -15030,7 +15030,7 @@
         <v>16499.04</v>
       </c>
     </row>
-    <row r="219" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:20" ns3:dyDescent="0.2">
       <c r="A219" t="s">
         <v>20</v>
       </c>
@@ -15096,7 +15096,7 @@
         <v>7342.9000000000015</v>
       </c>
     </row>
-    <row r="220" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:20" ns3:dyDescent="0.2">
       <c r="A220" t="s">
         <v>20</v>
       </c>
@@ -15162,7 +15162,7 @@
         <v>11106.099999999999</v>
       </c>
     </row>
-    <row r="221" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:20" ns3:dyDescent="0.2">
       <c r="A221" t="s">
         <v>28</v>
       </c>
@@ -15228,7 +15228,7 @@
         <v>3504.8199999999997</v>
       </c>
     </row>
-    <row r="222" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:20" ns3:dyDescent="0.2">
       <c r="A222" t="s">
         <v>26</v>
       </c>
@@ -15294,7 +15294,7 @@
         <v>116604</v>
       </c>
     </row>
-    <row r="223" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:20" ns3:dyDescent="0.2">
       <c r="A223" t="s">
         <v>28</v>
       </c>
@@ -15360,7 +15360,7 @@
         <v>141740</v>
       </c>
     </row>
-    <row r="224" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:20" ns3:dyDescent="0.2">
       <c r="A224" t="s">
         <v>35</v>
       </c>
@@ -15426,7 +15426,7 @@
         <v>15666</v>
       </c>
     </row>
-    <row r="225" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:20" ns3:dyDescent="0.2">
       <c r="A225" t="s">
         <v>35</v>
       </c>
@@ -15492,7 +15492,7 @@
         <v>9374.4</v>
       </c>
     </row>
-    <row r="226" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:20" ns3:dyDescent="0.2">
       <c r="A226" t="s">
         <v>28</v>
       </c>
@@ -15558,7 +15558,7 @@
         <v>11727</v>
       </c>
     </row>
-    <row r="227" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:20" ns3:dyDescent="0.2">
       <c r="A227" t="s">
         <v>30</v>
       </c>
@@ -15624,7 +15624,7 @@
         <v>-1008.75</v>
       </c>
     </row>
-    <row r="228" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:20" ns3:dyDescent="0.2">
       <c r="A228" t="s">
         <v>28</v>
       </c>
@@ -15690,7 +15690,7 @@
         <v>97875</v>
       </c>
     </row>
-    <row r="229" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:20" ns3:dyDescent="0.2">
       <c r="A229" t="s">
         <v>30</v>
       </c>
@@ -15756,7 +15756,7 @@
         <v>-2380</v>
       </c>
     </row>
-    <row r="230" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:20" ns3:dyDescent="0.2">
       <c r="A230" t="s">
         <v>30</v>
       </c>
@@ -15822,7 +15822,7 @@
         <v>-6887.5</v>
       </c>
     </row>
-    <row r="231" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:20" ns3:dyDescent="0.2">
       <c r="A231" t="s">
         <v>35</v>
       </c>
@@ -15888,7 +15888,7 @@
         <v>5932.32</v>
       </c>
     </row>
-    <row r="232" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:20" ns3:dyDescent="0.2">
       <c r="A232" t="s">
         <v>26</v>
       </c>
@@ -15954,7 +15954,7 @@
         <v>27811</v>
       </c>
     </row>
-    <row r="233" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:20" ns3:dyDescent="0.2">
       <c r="A233" t="s">
         <v>26</v>
       </c>
@@ -16020,7 +16020,7 @@
         <v>79663</v>
       </c>
     </row>
-    <row r="234" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:20" ns3:dyDescent="0.2">
       <c r="A234" t="s">
         <v>28</v>
       </c>
@@ -16086,7 +16086,7 @@
         <v>702.72000000000025</v>
       </c>
     </row>
-    <row r="235" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:20" ns3:dyDescent="0.2">
       <c r="A235" t="s">
         <v>26</v>
       </c>
@@ -16152,7 +16152,7 @@
         <v>61157</v>
       </c>
     </row>
-    <row r="236" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:20" ns3:dyDescent="0.2">
       <c r="A236" t="s">
         <v>28</v>
       </c>
@@ -16218,7 +16218,7 @@
         <v>123200</v>
       </c>
     </row>
-    <row r="237" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:20" ns3:dyDescent="0.2">
       <c r="A237" t="s">
         <v>35</v>
       </c>
@@ -16284,7 +16284,7 @@
         <v>14876.16</v>
       </c>
     </row>
-    <row r="238" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:20" ns3:dyDescent="0.2">
       <c r="A238" t="s">
         <v>28</v>
       </c>
@@ -16350,7 +16350,7 @@
         <v>12960</v>
       </c>
     </row>
-    <row r="239" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:20" ns3:dyDescent="0.2">
       <c r="A239" t="s">
         <v>28</v>
       </c>
@@ -16416,7 +16416,7 @@
         <v>1414.8199999999997</v>
       </c>
     </row>
-    <row r="240" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:20" ns3:dyDescent="0.2">
       <c r="A240" t="s">
         <v>28</v>
       </c>
@@ -16482,7 +16482,7 @@
         <v>19543.400000000001</v>
       </c>
     </row>
-    <row r="241" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:20" ns3:dyDescent="0.2">
       <c r="A241" t="s">
         <v>28</v>
       </c>
@@ -16548,7 +16548,7 @@
         <v>20039.199999999997</v>
       </c>
     </row>
-    <row r="242" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:20" ns3:dyDescent="0.2">
       <c r="A242" t="s">
         <v>28</v>
       </c>
@@ -16614,7 +16614,7 @@
         <v>298.86000000000013</v>
       </c>
     </row>
-    <row r="243" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:20" ns3:dyDescent="0.2">
       <c r="A243" t="s">
         <v>20</v>
       </c>
@@ -16680,7 +16680,7 @@
         <v>806.19999999999982</v>
       </c>
     </row>
-    <row r="244" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:20" ns3:dyDescent="0.2">
       <c r="A244" t="s">
         <v>28</v>
       </c>
@@ -16746,7 +16746,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="245" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:20" ns3:dyDescent="0.2">
       <c r="A245" t="s">
         <v>30</v>
       </c>
@@ -16812,7 +16812,7 @@
         <v>-19687.5</v>
       </c>
     </row>
-    <row r="246" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:20" ns3:dyDescent="0.2">
       <c r="A246" t="s">
         <v>28</v>
       </c>
@@ -16878,7 +16878,7 @@
         <v>1299.6000000000004</v>
       </c>
     </row>
-    <row r="247" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:20" ns3:dyDescent="0.2">
       <c r="A247" t="s">
         <v>20</v>
       </c>
@@ -16944,7 +16944,7 @@
         <v>4605</v>
       </c>
     </row>
-    <row r="248" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:20" ns3:dyDescent="0.2">
       <c r="A248" t="s">
         <v>35</v>
       </c>
@@ -17010,7 +17010,7 @@
         <v>19449</v>
       </c>
     </row>
-    <row r="249" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:20" ns3:dyDescent="0.2">
       <c r="A249" t="s">
         <v>28</v>
       </c>
@@ -17076,7 +17076,7 @@
         <v>2559.1800000000003</v>
       </c>
     </row>
-    <row r="250" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:20" ns3:dyDescent="0.2">
       <c r="A250" t="s">
         <v>28</v>
       </c>
@@ -17142,7 +17142,7 @@
         <v>104665</v>
       </c>
     </row>
-    <row r="251" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:20" ns3:dyDescent="0.2">
       <c r="A251" t="s">
         <v>20</v>
       </c>
@@ -17208,7 +17208,7 @@
         <v>10737.900000000001</v>
       </c>
     </row>
-    <row r="252" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:20" ns3:dyDescent="0.2">
       <c r="A252" t="s">
         <v>28</v>
       </c>
@@ -17274,7 +17274,7 @@
         <v>507.58999999999992</v>
       </c>
     </row>
-    <row r="253" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:20" ns3:dyDescent="0.2">
       <c r="A253" t="s">
         <v>26</v>
       </c>
@@ -17340,7 +17340,7 @@
         <v>11396</v>
       </c>
     </row>
-    <row r="254" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:20" ns3:dyDescent="0.2">
       <c r="A254" t="s">
         <v>26</v>
       </c>
@@ -17406,7 +17406,7 @@
         <v>48444</v>
       </c>
     </row>
-    <row r="255" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:20" ns3:dyDescent="0.2">
       <c r="A255" t="s">
         <v>30</v>
       </c>
@@ -17472,7 +17472,7 @@
         <v>2217.5</v>
       </c>
     </row>
-    <row r="256" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:20" ns3:dyDescent="0.2">
       <c r="A256" t="s">
         <v>20</v>
       </c>
@@ -17538,7 +17538,7 @@
         <v>8654.7999999999993</v>
       </c>
     </row>
-    <row r="257" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:20" ns3:dyDescent="0.2">
       <c r="A257" t="s">
         <v>30</v>
       </c>
@@ -17604,7 +17604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:20" ns3:dyDescent="0.2">
       <c r="A258" t="s">
         <v>35</v>
       </c>
@@ -17670,7 +17670,7 @@
         <v>12481.8</v>
       </c>
     </row>
-    <row r="259" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:20" ns3:dyDescent="0.2">
       <c r="A259" t="s">
         <v>30</v>
       </c>
@@ -17736,7 +17736,7 @@
         <v>-3740</v>
       </c>
     </row>
-    <row r="260" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:20" ns3:dyDescent="0.2">
       <c r="A260" t="s">
         <v>30</v>
       </c>
@@ -17802,7 +17802,7 @@
         <v>-2981.25</v>
       </c>
     </row>
-    <row r="261" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:20" ns3:dyDescent="0.2">
       <c r="A261" t="s">
         <v>28</v>
       </c>
@@ -17868,7 +17868,7 @@
         <v>115345.5</v>
       </c>
     </row>
-    <row r="262" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:20" ns3:dyDescent="0.2">
       <c r="A262" t="s">
         <v>20</v>
       </c>
@@ -17934,7 +17934,7 @@
         <v>9503.8000000000029</v>
       </c>
     </row>
-    <row r="263" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:20" ns3:dyDescent="0.2">
       <c r="A263" t="s">
         <v>30</v>
       </c>
@@ -18000,7 +18000,7 @@
         <v>-5570</v>
       </c>
     </row>
-    <row r="264" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:20" ns3:dyDescent="0.2">
       <c r="A264" t="s">
         <v>35</v>
       </c>
@@ -18066,7 +18066,7 @@
         <v>4807.92</v>
       </c>
     </row>
-    <row r="265" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:20" ns3:dyDescent="0.2">
       <c r="A265" t="s">
         <v>28</v>
       </c>
@@ -18132,7 +18132,7 @@
         <v>7978.5999999999985</v>
       </c>
     </row>
-    <row r="266" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:20" ns3:dyDescent="0.2">
       <c r="A266" t="s">
         <v>35</v>
       </c>
@@ -18198,7 +18198,7 @@
         <v>15578.64</v>
       </c>
     </row>
-    <row r="267" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:20" ns3:dyDescent="0.2">
       <c r="A267" t="s">
         <v>28</v>
       </c>
@@ -18264,7 +18264,7 @@
         <v>15632</v>
       </c>
     </row>
-    <row r="268" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:20" ns3:dyDescent="0.2">
       <c r="A268" t="s">
         <v>26</v>
       </c>
@@ -18330,7 +18330,7 @@
         <v>59860</v>
       </c>
     </row>
-    <row r="269" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:20" ns3:dyDescent="0.2">
       <c r="A269" t="s">
         <v>28</v>
       </c>
@@ -18396,7 +18396,7 @@
         <v>1942.17</v>
       </c>
     </row>
-    <row r="270" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:20" ns3:dyDescent="0.2">
       <c r="A270" t="s">
         <v>28</v>
       </c>
@@ -18462,7 +18462,7 @@
         <v>40788</v>
       </c>
     </row>
-    <row r="271" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:20" ns3:dyDescent="0.2">
       <c r="A271" t="s">
         <v>28</v>
       </c>
@@ -18528,7 +18528,7 @@
         <v>8751.5999999999985</v>
       </c>
     </row>
-    <row r="272" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:20" ns3:dyDescent="0.2">
       <c r="A272" t="s">
         <v>20</v>
       </c>
@@ -18594,7 +18594,7 @@
         <v>2166.3999999999996</v>
       </c>
     </row>
-    <row r="273" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:20" ns3:dyDescent="0.2">
       <c r="A273" t="s">
         <v>28</v>
       </c>
@@ -18660,7 +18660,7 @@
         <v>1729.5599999999995</v>
       </c>
     </row>
-    <row r="274" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:20" ns3:dyDescent="0.2">
       <c r="A274" t="s">
         <v>28</v>
       </c>
@@ -18726,7 +18726,7 @@
         <v>41073.5</v>
       </c>
     </row>
-    <row r="275" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:20" ns3:dyDescent="0.2">
       <c r="A275" t="s">
         <v>28</v>
       </c>
@@ -18792,7 +18792,7 @@
         <v>79655</v>
       </c>
     </row>
-    <row r="276" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:20" ns3:dyDescent="0.2">
       <c r="A276" t="s">
         <v>28</v>
       </c>
@@ -18858,7 +18858,7 @@
         <v>17481.599999999999</v>
       </c>
     </row>
-    <row r="277" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:20" ns3:dyDescent="0.2">
       <c r="A277" t="s">
         <v>28</v>
       </c>
@@ -18924,7 +18924,7 @@
         <v>2961.0600000000013</v>
       </c>
     </row>
-    <row r="278" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:20" ns3:dyDescent="0.2">
       <c r="A278" t="s">
         <v>26</v>
       </c>
@@ -18990,7 +18990,7 @@
         <v>7104</v>
       </c>
     </row>
-    <row r="279" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:20" ns3:dyDescent="0.2">
       <c r="A279" t="s">
         <v>28</v>
       </c>
@@ -19056,7 +19056,7 @@
         <v>8106</v>
       </c>
     </row>
-    <row r="280" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:20" ns3:dyDescent="0.2">
       <c r="A280" t="s">
         <v>35</v>
       </c>
@@ -19122,7 +19122,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="281" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:20" ns3:dyDescent="0.2">
       <c r="A281" t="s">
         <v>26</v>
       </c>
@@ -19188,7 +19188,7 @@
         <v>12375</v>
       </c>
     </row>
-    <row r="282" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:20" ns3:dyDescent="0.2">
       <c r="A282" t="s">
         <v>35</v>
       </c>
@@ -19254,7 +19254,7 @@
         <v>25542</v>
       </c>
     </row>
-    <row r="283" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:20" ns3:dyDescent="0.2">
       <c r="A283" t="s">
         <v>35</v>
       </c>
@@ -19320,7 +19320,7 @@
         <v>17577</v>
       </c>
     </row>
-    <row r="284" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:20" ns3:dyDescent="0.2">
       <c r="A284" t="s">
         <v>30</v>
       </c>
@@ -19386,7 +19386,7 @@
         <v>21097.5</v>
       </c>
     </row>
-    <row r="285" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:20" ns3:dyDescent="0.2">
       <c r="A285" t="s">
         <v>26</v>
       </c>
@@ -19452,7 +19452,7 @@
         <v>108147</v>
       </c>
     </row>
-    <row r="286" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:20" ns3:dyDescent="0.2">
       <c r="A286" t="s">
         <v>28</v>
       </c>
@@ -19518,7 +19518,7 @@
         <v>8670.5250000000015</v>
       </c>
     </row>
-    <row r="287" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:20" ns3:dyDescent="0.2">
       <c r="A287" t="s">
         <v>28</v>
       </c>
@@ -19584,7 +19584,7 @@
         <v>37867.199999999997</v>
       </c>
     </row>
-    <row r="288" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:20" ns3:dyDescent="0.2">
       <c r="A288" t="s">
         <v>28</v>
       </c>
@@ -19650,7 +19650,7 @@
         <v>81612.75</v>
       </c>
     </row>
-    <row r="289" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:20" ns3:dyDescent="0.2">
       <c r="A289" t="s">
         <v>30</v>
       </c>
@@ -19716,7 +19716,7 @@
         <v>1856.25</v>
       </c>
     </row>
-    <row r="290" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:20" ns3:dyDescent="0.2">
       <c r="A290" t="s">
         <v>30</v>
       </c>
@@ -19782,7 +19782,7 @@
         <v>5304.375</v>
       </c>
     </row>
-    <row r="291" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:20" ns3:dyDescent="0.2">
       <c r="A291" t="s">
         <v>28</v>
       </c>
@@ -19848,7 +19848,7 @@
         <v>24252</v>
       </c>
     </row>
-    <row r="292" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:20" ns3:dyDescent="0.2">
       <c r="A292" t="s">
         <v>35</v>
       </c>
@@ -19914,7 +19914,7 @@
         <v>16554.240000000002</v>
       </c>
     </row>
-    <row r="293" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:20" ns3:dyDescent="0.2">
       <c r="A293" t="s">
         <v>28</v>
       </c>
@@ -19980,7 +19980,7 @@
         <v>36194.699999999997</v>
       </c>
     </row>
-    <row r="294" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:20" ns3:dyDescent="0.2">
       <c r="A294" t="s">
         <v>26</v>
       </c>
@@ -20046,7 +20046,7 @@
         <v>53751</v>
       </c>
     </row>
-    <row r="295" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:20" ns3:dyDescent="0.2">
       <c r="A295" t="s">
         <v>30</v>
       </c>
@@ -20112,7 +20112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:20" ns3:dyDescent="0.2">
       <c r="A296" t="s">
         <v>26</v>
       </c>
@@ -20178,7 +20178,7 @@
         <v>56245</v>
       </c>
     </row>
-    <row r="297" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:20" ns3:dyDescent="0.2">
       <c r="A297" t="s">
         <v>20</v>
       </c>
@@ -20244,7 +20244,7 @@
         <v>15584.099999999999</v>
       </c>
     </row>
-    <row r="298" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:20" ns3:dyDescent="0.2">
       <c r="A298" t="s">
         <v>28</v>
       </c>
@@ -20310,7 +20310,7 @@
         <v>67620</v>
       </c>
     </row>
-    <row r="299" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:20" ns3:dyDescent="0.2">
       <c r="A299" t="s">
         <v>35</v>
       </c>
@@ -20376,7 +20376,7 @@
         <v>14186.16</v>
       </c>
     </row>
-    <row r="300" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:20" ns3:dyDescent="0.2">
       <c r="A300" t="s">
         <v>28</v>
       </c>
@@ -20442,7 +20442,7 @@
         <v>1812.96</v>
       </c>
     </row>
-    <row r="301" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:20" ns3:dyDescent="0.2">
       <c r="A301" t="s">
         <v>28</v>
       </c>
@@ -20508,7 +20508,7 @@
         <v>35619</v>
       </c>
     </row>
-    <row r="302" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:20" ns3:dyDescent="0.2">
       <c r="A302" t="s">
         <v>26</v>
       </c>
@@ -20574,7 +20574,7 @@
         <v>87457.5</v>
       </c>
     </row>
-    <row r="303" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:20" ns3:dyDescent="0.2">
       <c r="A303" t="s">
         <v>20</v>
       </c>
@@ -20640,7 +20640,7 @@
         <v>13413.75</v>
       </c>
     </row>
-    <row r="304" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:20" ns3:dyDescent="0.2">
       <c r="A304" t="s">
         <v>28</v>
       </c>
@@ -20706,7 +20706,7 @@
         <v>79062.75</v>
       </c>
     </row>
-    <row r="305" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:20" ns3:dyDescent="0.2">
       <c r="A305" t="s">
         <v>20</v>
       </c>
@@ -20772,7 +20772,7 @@
         <v>9592.1999999999971</v>
       </c>
     </row>
-    <row r="306" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:20" ns3:dyDescent="0.2">
       <c r="A306" t="s">
         <v>30</v>
       </c>
@@ -20838,7 +20838,7 @@
         <v>-25841.25</v>
       </c>
     </row>
-    <row r="307" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:20" ns3:dyDescent="0.2">
       <c r="A307" t="s">
         <v>20</v>
       </c>
@@ -20904,7 +20904,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="308" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:20" ns3:dyDescent="0.2">
       <c r="A308" t="s">
         <v>35</v>
       </c>
@@ -20970,7 +20970,7 @@
         <v>27459.9</v>
       </c>
     </row>
-    <row r="309" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:20" ns3:dyDescent="0.2">
       <c r="A309" t="s">
         <v>28</v>
       </c>
@@ -21036,7 +21036,7 @@
         <v>3114.3600000000006</v>
       </c>
     </row>
-    <row r="310" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:20" ns3:dyDescent="0.2">
       <c r="A310" t="s">
         <v>26</v>
       </c>
@@ -21102,7 +21102,7 @@
         <v>24822</v>
       </c>
     </row>
-    <row r="311" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:20" ns3:dyDescent="0.2">
       <c r="A311" t="s">
         <v>28</v>
       </c>
@@ -21168,7 +21168,7 @@
         <v>18568.800000000003</v>
       </c>
     </row>
-    <row r="312" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:20" ns3:dyDescent="0.2">
       <c r="A312" t="s">
         <v>28</v>
       </c>
@@ -21234,7 +21234,7 @@
         <v>49159</v>
       </c>
     </row>
-    <row r="313" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:20" ns3:dyDescent="0.2">
       <c r="A313" t="s">
         <v>28</v>
       </c>
@@ -21300,7 +21300,7 @@
         <v>4363.2000000000007</v>
       </c>
     </row>
-    <row r="314" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:20" ns3:dyDescent="0.2">
       <c r="A314" t="s">
         <v>20</v>
       </c>
@@ -21366,7 +21366,7 @@
         <v>4438.5</v>
       </c>
     </row>
-    <row r="315" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:20" ns3:dyDescent="0.2">
       <c r="A315" t="s">
         <v>28</v>
       </c>
@@ -21432,7 +21432,7 @@
         <v>2408.25</v>
       </c>
     </row>
-    <row r="316" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:20" ns3:dyDescent="0.2">
       <c r="A316" t="s">
         <v>28</v>
       </c>
@@ -21498,7 +21498,7 @@
         <v>686.85000000000036</v>
       </c>
     </row>
-    <row r="317" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:20" ns3:dyDescent="0.2">
       <c r="A317" t="s">
         <v>28</v>
       </c>
@@ -21564,7 +21564,7 @@
         <v>1987.8999999999996</v>
       </c>
     </row>
-    <row r="318" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:20" ns3:dyDescent="0.2">
       <c r="A318" t="s">
         <v>28</v>
       </c>
@@ -21630,7 +21630,7 @@
         <v>698.65999999999985</v>
       </c>
     </row>
-    <row r="319" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:20" ns3:dyDescent="0.2">
       <c r="A319" t="s">
         <v>26</v>
       </c>
@@ -21696,7 +21696,7 @@
         <v>40392</v>
       </c>
     </row>
-    <row r="320" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:20" ns3:dyDescent="0.2">
       <c r="A320" t="s">
         <v>26</v>
       </c>
@@ -21762,7 +21762,7 @@
         <v>76032</v>
       </c>
     </row>
-    <row r="321" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:20" ns3:dyDescent="0.2">
       <c r="A321" t="s">
         <v>30</v>
       </c>
@@ -21828,7 +21828,7 @@
         <v>5690</v>
       </c>
     </row>
-    <row r="322" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:20" ns3:dyDescent="0.2">
       <c r="A322" t="s">
         <v>28</v>
       </c>
@@ -21894,7 +21894,7 @@
         <v>7811.4</v>
       </c>
     </row>
-    <row r="323" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:20" ns3:dyDescent="0.2">
       <c r="A323" t="s">
         <v>26</v>
       </c>
@@ -21960,7 +21960,7 @@
         <v>110884</v>
       </c>
     </row>
-    <row r="324" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:20" ns3:dyDescent="0.2">
       <c r="A324" t="s">
         <v>35</v>
       </c>
@@ -22026,7 +22026,7 @@
         <v>7378.32</v>
       </c>
     </row>
-    <row r="325" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:20" ns3:dyDescent="0.2">
       <c r="A325" t="s">
         <v>28</v>
       </c>
@@ -22092,7 +22092,7 @@
         <v>14067</v>
       </c>
     </row>
-    <row r="326" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:20" ns3:dyDescent="0.2">
       <c r="A326" t="s">
         <v>28</v>
       </c>
@@ -22158,7 +22158,7 @@
         <v>3839.5499999999993</v>
       </c>
     </row>
-    <row r="327" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:20" ns3:dyDescent="0.2">
       <c r="A327" t="s">
         <v>28</v>
       </c>
@@ -22224,7 +22224,7 @@
         <v>100740</v>
       </c>
     </row>
-    <row r="328" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:20" ns3:dyDescent="0.2">
       <c r="A328" t="s">
         <v>20</v>
       </c>
@@ -22290,7 +22290,7 @@
         <v>6273</v>
       </c>
     </row>
-    <row r="329" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:20" ns3:dyDescent="0.2">
       <c r="A329" t="s">
         <v>20</v>
       </c>
@@ -22356,7 +22356,7 @@
         <v>4984.9000000000015</v>
       </c>
     </row>
-    <row r="330" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:20" ns3:dyDescent="0.2">
       <c r="A330" t="s">
         <v>26</v>
       </c>
@@ -22422,7 +22422,7 @@
         <v>49358</v>
       </c>
     </row>
-    <row r="331" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:20" ns3:dyDescent="0.2">
       <c r="A331" t="s">
         <v>30</v>
       </c>
@@ -22488,7 +22488,7 @@
         <v>-6168.75</v>
       </c>
     </row>
-    <row r="332" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:20" ns3:dyDescent="0.2">
       <c r="A332" t="s">
         <v>28</v>
       </c>
@@ -22554,7 +22554,7 @@
         <v>370.07999999999993</v>
       </c>
     </row>
-    <row r="333" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:20" ns3:dyDescent="0.2">
       <c r="A333" t="s">
         <v>28</v>
       </c>
@@ -22620,7 +22620,7 @@
         <v>1576.8000000000002</v>
       </c>
     </row>
-    <row r="334" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:20" ns3:dyDescent="0.2">
       <c r="A334" t="s">
         <v>28</v>
       </c>
@@ -22686,7 +22686,7 @@
         <v>97461</v>
       </c>
     </row>
-    <row r="335" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:20" ns3:dyDescent="0.2">
       <c r="A335" t="s">
         <v>20</v>
       </c>
@@ -22752,7 +22752,7 @@
         <v>894.25</v>
       </c>
     </row>
-    <row r="336" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:20" ns3:dyDescent="0.2">
       <c r="A336" t="s">
         <v>35</v>
       </c>
@@ -22818,7 +22818,7 @@
         <v>6969.6</v>
       </c>
     </row>
-    <row r="337" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:20" ns3:dyDescent="0.2">
       <c r="A337" t="s">
         <v>28</v>
       </c>
@@ -22884,7 +22884,7 @@
         <v>5436.6</v>
       </c>
     </row>
-    <row r="338" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:20" ns3:dyDescent="0.2">
       <c r="A338" t="s">
         <v>28</v>
       </c>
@@ -22950,7 +22950,7 @@
         <v>127215</v>
       </c>
     </row>
-    <row r="339" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:20" ns3:dyDescent="0.2">
       <c r="A339" t="s">
         <v>26</v>
       </c>
@@ -23016,7 +23016,7 @@
         <v>11820</v>
       </c>
     </row>
-    <row r="340" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:20" ns3:dyDescent="0.2">
       <c r="A340" t="s">
         <v>20</v>
       </c>
@@ -23082,7 +23082,7 @@
         <v>2765</v>
       </c>
     </row>
-    <row r="341" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:20" ns3:dyDescent="0.2">
       <c r="A341" t="s">
         <v>30</v>
       </c>
@@ -23148,7 +23148,7 @@
         <v>-2557.5</v>
       </c>
     </row>
-    <row r="342" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:20" ns3:dyDescent="0.2">
       <c r="A342" t="s">
         <v>28</v>
       </c>
@@ -23214,7 +23214,7 @@
         <v>16312</v>
       </c>
     </row>
-    <row r="343" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:20" ns3:dyDescent="0.2">
       <c r="A343" t="s">
         <v>30</v>
       </c>
@@ -23280,7 +23280,7 @@
         <v>-12538.75</v>
       </c>
     </row>
-    <row r="344" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:20" ns3:dyDescent="0.2">
       <c r="A344" t="s">
         <v>35</v>
       </c>
@@ -23346,7 +23346,7 @@
         <v>15944.04</v>
       </c>
     </row>
-    <row r="345" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:20" ns3:dyDescent="0.2">
       <c r="A345" t="s">
         <v>35</v>
       </c>
@@ -23412,7 +23412,7 @@
         <v>20117.16</v>
       </c>
     </row>
-    <row r="346" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:20" ns3:dyDescent="0.2">
       <c r="A346" t="s">
         <v>28</v>
       </c>
@@ -23478,7 +23478,7 @@
         <v>12549.599999999999</v>
       </c>
     </row>
-    <row r="347" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:20" ns3:dyDescent="0.2">
       <c r="A347" t="s">
         <v>28</v>
       </c>
@@ -23544,7 +23544,7 @@
         <v>8200</v>
       </c>
     </row>
-    <row r="348" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:20" ns3:dyDescent="0.2">
       <c r="A348" t="s">
         <v>30</v>
       </c>
@@ -23610,7 +23610,7 @@
         <v>-35550</v>
       </c>
     </row>
-    <row r="349" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:20" ns3:dyDescent="0.2">
       <c r="A349" t="s">
         <v>28</v>
       </c>
@@ -23676,7 +23676,7 @@
         <v>106912.5</v>
       </c>
     </row>
-    <row r="350" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:20" ns3:dyDescent="0.2">
       <c r="A350" t="s">
         <v>20</v>
       </c>
@@ -23742,7 +23742,7 @@
         <v>7771.5</v>
       </c>
     </row>
-    <row r="351" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:20" ns3:dyDescent="0.2">
       <c r="A351" t="s">
         <v>35</v>
       </c>
@@ -23808,7 +23808,7 @@
         <v>13003.2</v>
       </c>
     </row>
-    <row r="352" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:20" ns3:dyDescent="0.2">
       <c r="A352" t="s">
         <v>20</v>
       </c>
@@ -23874,7 +23874,7 @@
         <v>10890</v>
       </c>
     </row>
-    <row r="353" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:20" ns3:dyDescent="0.2">
       <c r="A353" t="s">
         <v>20</v>
       </c>
@@ -23940,7 +23940,7 @@
         <v>4440</v>
       </c>
     </row>
-    <row r="354" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:20" ns3:dyDescent="0.2">
       <c r="A354" t="s">
         <v>20</v>
       </c>
@@ -24006,7 +24006,7 @@
         <v>12350</v>
       </c>
     </row>
-    <row r="355" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:20" ns3:dyDescent="0.2">
       <c r="A355" t="s">
         <v>35</v>
       </c>
@@ -24072,7 +24072,7 @@
         <v>22662</v>
       </c>
     </row>
-    <row r="356" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:20" ns3:dyDescent="0.2">
       <c r="A356" t="s">
         <v>28</v>
       </c>
@@ -24138,7 +24138,7 @@
         <v>18990</v>
       </c>
     </row>
-    <row r="357" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:20" ns3:dyDescent="0.2">
       <c r="A357" t="s">
         <v>35</v>
       </c>
@@ -24204,7 +24204,7 @@
         <v>13905</v>
       </c>
     </row>
-    <row r="358" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:20" ns3:dyDescent="0.2">
       <c r="A358" t="s">
         <v>20</v>
       </c>
@@ -24270,7 +24270,7 @@
         <v>12350</v>
       </c>
     </row>
-    <row r="359" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:20" ns3:dyDescent="0.2">
       <c r="A359" t="s">
         <v>35</v>
       </c>
@@ -24336,7 +24336,7 @@
         <v>22662</v>
       </c>
     </row>
-    <row r="360" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:20" ns3:dyDescent="0.2">
       <c r="A360" t="s">
         <v>28</v>
       </c>
@@ -24402,7 +24402,7 @@
         <v>90540</v>
       </c>
     </row>
-    <row r="361" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:20" ns3:dyDescent="0.2">
       <c r="A361" t="s">
         <v>28</v>
       </c>
@@ -24468,7 +24468,7 @@
         <v>90540</v>
       </c>
     </row>
-    <row r="362" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:20" ns3:dyDescent="0.2">
       <c r="A362" t="s">
         <v>35</v>
       </c>
@@ -24534,7 +24534,7 @@
         <v>13905</v>
       </c>
     </row>
-    <row r="363" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:20" ns3:dyDescent="0.2">
       <c r="A363" t="s">
         <v>20</v>
       </c>
@@ -24600,7 +24600,7 @@
         <v>10890</v>
       </c>
     </row>
-    <row r="364" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:20" ns3:dyDescent="0.2">
       <c r="A364" t="s">
         <v>20</v>
       </c>
@@ -24666,7 +24666,7 @@
         <v>4440</v>
       </c>
     </row>
-    <row r="365" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:20" ns3:dyDescent="0.2">
       <c r="A365" t="s">
         <v>28</v>
       </c>
@@ -24732,7 +24732,7 @@
         <v>18990</v>
       </c>
     </row>
-    <row r="366" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:20" ns3:dyDescent="0.2">
       <c r="A366" t="s">
         <v>30</v>
       </c>
@@ -24798,7 +24798,7 @@
         <v>2726.25</v>
       </c>
     </row>
-    <row r="367" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:20" ns3:dyDescent="0.2">
       <c r="A367" t="s">
         <v>30</v>
       </c>
@@ -24864,7 +24864,7 @@
         <v>2951.25</v>
       </c>
     </row>
-    <row r="368" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:20" ns3:dyDescent="0.2">
       <c r="A368" t="s">
         <v>30</v>
       </c>
@@ -24930,7 +24930,7 @@
         <v>2726.25</v>
       </c>
     </row>
-    <row r="369" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:20" ns3:dyDescent="0.2">
       <c r="A369" t="s">
         <v>30</v>
       </c>
@@ -24996,7 +24996,7 @@
         <v>2951.25</v>
       </c>
     </row>
-    <row r="370" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:20" ns3:dyDescent="0.2">
       <c r="A370" t="s">
         <v>35</v>
       </c>
@@ -25062,7 +25062,7 @@
         <v>10003.92</v>
       </c>
     </row>
-    <row r="371" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:20" ns3:dyDescent="0.2">
       <c r="A371" t="s">
         <v>35</v>
       </c>
@@ -25128,7 +25128,7 @@
         <v>10003.92</v>
       </c>
     </row>
-    <row r="372" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:20" ns3:dyDescent="0.2">
       <c r="A372" t="s">
         <v>30</v>
       </c>
@@ -25194,7 +25194,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="373" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:20" ns3:dyDescent="0.2">
       <c r="A373" t="s">
         <v>30</v>
       </c>
@@ -25260,7 +25260,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="374" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:20" ns3:dyDescent="0.2">
       <c r="A374" t="s">
         <v>26</v>
       </c>
@@ -25326,7 +25326,7 @@
         <v>28249</v>
       </c>
     </row>
-    <row r="375" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:20" ns3:dyDescent="0.2">
       <c r="A375" t="s">
         <v>35</v>
       </c>
@@ -25392,7 +25392,7 @@
         <v>16424.64</v>
       </c>
     </row>
-    <row r="376" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:20" ns3:dyDescent="0.2">
       <c r="A376" t="s">
         <v>35</v>
       </c>
@@ -25458,7 +25458,7 @@
         <v>16424.64</v>
       </c>
     </row>
-    <row r="377" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:20" ns3:dyDescent="0.2">
       <c r="A377" t="s">
         <v>26</v>
       </c>
@@ -25524,7 +25524,7 @@
         <v>28249</v>
       </c>
     </row>
-    <row r="378" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:20" ns3:dyDescent="0.2">
       <c r="A378" t="s">
         <v>30</v>
       </c>
@@ -25590,7 +25590,7 @@
         <v>1962.5</v>
       </c>
     </row>
-    <row r="379" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:20" ns3:dyDescent="0.2">
       <c r="A379" t="s">
         <v>30</v>
       </c>
@@ -25656,7 +25656,7 @@
         <v>1962.5</v>
       </c>
     </row>
-    <row r="380" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:20" ns3:dyDescent="0.2">
       <c r="A380" t="s">
         <v>26</v>
       </c>
@@ -25722,7 +25722,7 @@
         <v>34685</v>
       </c>
     </row>
-    <row r="381" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:20" ns3:dyDescent="0.2">
       <c r="A381" t="s">
         <v>26</v>
       </c>
@@ -25788,7 +25788,7 @@
         <v>34685</v>
       </c>
     </row>
-    <row r="382" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:20" ns3:dyDescent="0.2">
       <c r="A382" t="s">
         <v>28</v>
       </c>
@@ -25854,7 +25854,7 @@
         <v>43645</v>
       </c>
     </row>
-    <row r="383" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:20" ns3:dyDescent="0.2">
       <c r="A383" t="s">
         <v>28</v>
       </c>
@@ -25920,7 +25920,7 @@
         <v>43645</v>
       </c>
     </row>
-    <row r="384" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:20" ns3:dyDescent="0.2">
       <c r="A384" t="s">
         <v>20</v>
       </c>
@@ -25986,7 +25986,7 @@
         <v>11660.400000000001</v>
       </c>
     </row>
-    <row r="385" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:20" ns3:dyDescent="0.2">
       <c r="A385" t="s">
         <v>28</v>
       </c>
@@ -26052,7 +26052,7 @@
         <v>103224</v>
       </c>
     </row>
-    <row r="386" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:20" ns3:dyDescent="0.2">
       <c r="A386" t="s">
         <v>28</v>
       </c>
@@ -26118,7 +26118,7 @@
         <v>103224</v>
       </c>
     </row>
-    <row r="387" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:20" ns3:dyDescent="0.2">
       <c r="A387" t="s">
         <v>28</v>
       </c>
@@ -26184,7 +26184,7 @@
         <v>2366.84</v>
       </c>
     </row>
-    <row r="388" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:20" ns3:dyDescent="0.2">
       <c r="A388" t="s">
         <v>20</v>
       </c>
@@ -26250,7 +26250,7 @@
         <v>11660.400000000001</v>
       </c>
     </row>
-    <row r="389" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:20" ns3:dyDescent="0.2">
       <c r="A389" t="s">
         <v>28</v>
       </c>
@@ -26316,7 +26316,7 @@
         <v>2366.84</v>
       </c>
     </row>
-    <row r="390" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:20" ns3:dyDescent="0.2">
       <c r="A390" t="s">
         <v>28</v>
       </c>
@@ -26382,7 +26382,7 @@
         <v>1713.8500000000004</v>
       </c>
     </row>
-    <row r="391" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:20" ns3:dyDescent="0.2">
       <c r="A391" t="s">
         <v>28</v>
       </c>
@@ -26448,7 +26448,7 @@
         <v>1713.8500000000004</v>
       </c>
     </row>
-    <row r="392" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:20" ns3:dyDescent="0.2">
       <c r="A392" t="s">
         <v>26</v>
       </c>
@@ -26514,7 +26514,7 @@
         <v>12992</v>
       </c>
     </row>
-    <row r="393" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:20" ns3:dyDescent="0.2">
       <c r="A393" t="s">
         <v>26</v>
       </c>
@@ -26580,7 +26580,7 @@
         <v>12992</v>
       </c>
     </row>
-    <row r="394" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:20" ns3:dyDescent="0.2">
       <c r="A394" t="s">
         <v>28</v>
       </c>
@@ -26646,7 +26646,7 @@
         <v>10768.8</v>
       </c>
     </row>
-    <row r="395" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:20" ns3:dyDescent="0.2">
       <c r="A395" t="s">
         <v>28</v>
       </c>
@@ -26712,7 +26712,7 @@
         <v>10768.8</v>
       </c>
     </row>
-    <row r="396" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:20" ns3:dyDescent="0.2">
       <c r="A396" t="s">
         <v>28</v>
       </c>
@@ -26778,7 +26778,7 @@
         <v>5947.2000000000007</v>
       </c>
     </row>
-    <row r="397" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:20" ns3:dyDescent="0.2">
       <c r="A397" t="s">
         <v>28</v>
       </c>
@@ -26844,7 +26844,7 @@
         <v>11474.400000000001</v>
       </c>
     </row>
-    <row r="398" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:20" ns3:dyDescent="0.2">
       <c r="A398" t="s">
         <v>26</v>
       </c>
@@ -26910,7 +26910,7 @@
         <v>63960</v>
       </c>
     </row>
-    <row r="399" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:20" ns3:dyDescent="0.2">
       <c r="A399" t="s">
         <v>28</v>
       </c>
@@ -26976,7 +26976,7 @@
         <v>4186.0800000000017</v>
       </c>
     </row>
-    <row r="400" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:20" ns3:dyDescent="0.2">
       <c r="A400" t="s">
         <v>28</v>
       </c>
@@ -27042,7 +27042,7 @@
         <v>3366.7199999999993</v>
       </c>
     </row>
-    <row r="401" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:20" ns3:dyDescent="0.2">
       <c r="A401" t="s">
         <v>28</v>
       </c>
@@ -27108,7 +27108,7 @@
         <v>3366.7199999999993</v>
       </c>
     </row>
-    <row r="402" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:20" ns3:dyDescent="0.2">
       <c r="A402" t="s">
         <v>28</v>
       </c>
@@ -27174,7 +27174,7 @@
         <v>5947.2000000000007</v>
       </c>
     </row>
-    <row r="403" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:20" ns3:dyDescent="0.2">
       <c r="A403" t="s">
         <v>28</v>
       </c>
@@ -27240,7 +27240,7 @@
         <v>4186.0800000000017</v>
       </c>
     </row>
-    <row r="404" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:20" ns3:dyDescent="0.2">
       <c r="A404" t="s">
         <v>28</v>
       </c>
@@ -27306,7 +27306,7 @@
         <v>11474.400000000001</v>
       </c>
     </row>
-    <row r="405" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:20" ns3:dyDescent="0.2">
       <c r="A405" t="s">
         <v>26</v>
       </c>
@@ -27372,7 +27372,7 @@
         <v>63960</v>
       </c>
     </row>
-    <row r="406" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:20" ns3:dyDescent="0.2">
       <c r="A406" t="s">
         <v>26</v>
       </c>
@@ -27438,7 +27438,7 @@
         <v>25162</v>
       </c>
     </row>
-    <row r="407" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:20" ns3:dyDescent="0.2">
       <c r="A407" t="s">
         <v>26</v>
       </c>
@@ -27504,7 +27504,7 @@
         <v>25162</v>
       </c>
     </row>
-    <row r="408" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:20" ns3:dyDescent="0.2">
       <c r="A408" t="s">
         <v>28</v>
       </c>
@@ -27570,7 +27570,7 @@
         <v>8511.5999999999985</v>
       </c>
     </row>
-    <row r="409" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:20" ns3:dyDescent="0.2">
       <c r="A409" t="s">
         <v>28</v>
       </c>
@@ -27636,7 +27636,7 @@
         <v>8511.5999999999985</v>
       </c>
     </row>
-    <row r="410" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:20" ns3:dyDescent="0.2">
       <c r="A410" t="s">
         <v>28</v>
       </c>
@@ -27702,7 +27702,7 @@
         <v>42528</v>
       </c>
     </row>
-    <row r="411" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:20" ns3:dyDescent="0.2">
       <c r="A411" t="s">
         <v>28</v>
       </c>
@@ -27768,7 +27768,7 @@
         <v>42528</v>
       </c>
     </row>
-    <row r="412" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:20" ns3:dyDescent="0.2">
       <c r="A412" t="s">
         <v>20</v>
       </c>
@@ -27834,7 +27834,7 @@
         <v>7829.3499999999985</v>
       </c>
     </row>
-    <row r="413" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:20" ns3:dyDescent="0.2">
       <c r="A413" t="s">
         <v>20</v>
       </c>
@@ -27900,7 +27900,7 @@
         <v>7829.3499999999985</v>
       </c>
     </row>
-    <row r="414" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:20" ns3:dyDescent="0.2">
       <c r="A414" t="s">
         <v>35</v>
       </c>
@@ -27966,7 +27966,7 @@
         <v>4493.76</v>
       </c>
     </row>
-    <row r="415" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:20" ns3:dyDescent="0.2">
       <c r="A415" t="s">
         <v>28</v>
       </c>
@@ -28032,7 +28032,7 @@
         <v>117124</v>
       </c>
     </row>
-    <row r="416" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:20" ns3:dyDescent="0.2">
       <c r="A416" t="s">
         <v>30</v>
       </c>
@@ -28098,7 +28098,7 @@
         <v>-17808.75</v>
       </c>
     </row>
-    <row r="417" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:20" ns3:dyDescent="0.2">
       <c r="A417" t="s">
         <v>28</v>
       </c>
@@ -28164,7 +28164,7 @@
         <v>117124</v>
       </c>
     </row>
-    <row r="418" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:20" ns3:dyDescent="0.2">
       <c r="A418" t="s">
         <v>28</v>
       </c>
@@ -28230,7 +28230,7 @@
         <v>1297.1000000000004</v>
       </c>
     </row>
-    <row r="419" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:20" ns3:dyDescent="0.2">
       <c r="A419" t="s">
         <v>35</v>
       </c>
@@ -28296,7 +28296,7 @@
         <v>4493.76</v>
       </c>
     </row>
-    <row r="420" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:20" ns3:dyDescent="0.2">
       <c r="A420" t="s">
         <v>30</v>
       </c>
@@ -28362,7 +28362,7 @@
         <v>-17808.75</v>
       </c>
     </row>
-    <row r="421" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:20" ns3:dyDescent="0.2">
       <c r="A421" t="s">
         <v>28</v>
       </c>
@@ -28428,7 +28428,7 @@
         <v>1297.1000000000004</v>
       </c>
     </row>
-    <row r="422" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:20" ns3:dyDescent="0.2">
       <c r="A422" t="s">
         <v>30</v>
       </c>
@@ -28494,7 +28494,7 @@
         <v>13327.5</v>
       </c>
     </row>
-    <row r="423" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:20" ns3:dyDescent="0.2">
       <c r="A423" t="s">
         <v>35</v>
       </c>
@@ -28560,7 +28560,7 @@
         <v>3303</v>
       </c>
     </row>
-    <row r="424" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:20" ns3:dyDescent="0.2">
       <c r="A424" t="s">
         <v>28</v>
       </c>
@@ -28626,7 +28626,7 @@
         <v>3372</v>
       </c>
     </row>
-    <row r="425" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:20" ns3:dyDescent="0.2">
       <c r="A425" t="s">
         <v>28</v>
       </c>
@@ -28692,7 +28692,7 @@
         <v>4880.9700000000012</v>
       </c>
     </row>
-    <row r="426" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:20" ns3:dyDescent="0.2">
       <c r="A426" t="s">
         <v>28</v>
       </c>
@@ -28758,7 +28758,7 @@
         <v>13479.900000000001</v>
       </c>
     </row>
-    <row r="427" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:20" ns3:dyDescent="0.2">
       <c r="A427" t="s">
         <v>30</v>
       </c>
@@ -28824,7 +28824,7 @@
         <v>6836.25</v>
       </c>
     </row>
-    <row r="428" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:20" ns3:dyDescent="0.2">
       <c r="A428" t="s">
         <v>35</v>
       </c>
@@ -28890,7 +28890,7 @@
         <v>11832.48</v>
       </c>
     </row>
-    <row r="429" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:20" ns3:dyDescent="0.2">
       <c r="A429" t="s">
         <v>28</v>
       </c>
@@ -28956,7 +28956,7 @@
         <v>262200</v>
       </c>
     </row>
-    <row r="430" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:20" ns3:dyDescent="0.2">
       <c r="A430" t="s">
         <v>30</v>
       </c>
@@ -29022,7 +29022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:20" ns3:dyDescent="0.2">
       <c r="A431" t="s">
         <v>28</v>
       </c>
@@ -29088,7 +29088,7 @@
         <v>2776.9500000000007</v>
       </c>
     </row>
-    <row r="432" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:20" ns3:dyDescent="0.2">
       <c r="A432" t="s">
         <v>30</v>
       </c>
@@ -29154,7 +29154,7 @@
         <v>-4533.75</v>
       </c>
     </row>
-    <row r="433" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:20" ns3:dyDescent="0.2">
       <c r="A433" t="s">
         <v>30</v>
       </c>
@@ -29220,7 +29220,7 @@
         <v>-13173.75</v>
       </c>
     </row>
-    <row r="434" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:20" ns3:dyDescent="0.2">
       <c r="A434" t="s">
         <v>26</v>
       </c>
@@ -29286,7 +29286,7 @@
         <v>48111</v>
       </c>
     </row>
-    <row r="435" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:20" ns3:dyDescent="0.2">
       <c r="A435" t="s">
         <v>28</v>
       </c>
@@ -29352,7 +29352,7 @@
         <v>5418</v>
       </c>
     </row>
-    <row r="436" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:20" ns3:dyDescent="0.2">
       <c r="A436" t="s">
         <v>28</v>
       </c>
@@ -29418,7 +29418,7 @@
         <v>3666.6000000000004</v>
       </c>
     </row>
-    <row r="437" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:20" ns3:dyDescent="0.2">
       <c r="A437" t="s">
         <v>26</v>
       </c>
@@ -29484,7 +29484,7 @@
         <v>87250.5</v>
       </c>
     </row>
-    <row r="438" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:20" ns3:dyDescent="0.2">
       <c r="A438" t="s">
         <v>28</v>
       </c>
@@ -29550,7 +29550,7 @@
         <v>76459.5</v>
       </c>
     </row>
-    <row r="439" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:20" ns3:dyDescent="0.2">
       <c r="A439" t="s">
         <v>28</v>
       </c>
@@ -29616,7 +29616,7 @@
         <v>1122.0299999999997</v>
       </c>
     </row>
-    <row r="440" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:20" ns3:dyDescent="0.2">
       <c r="A440" t="s">
         <v>20</v>
       </c>
@@ -29682,7 +29682,7 @@
         <v>5951.3250000000007</v>
       </c>
     </row>
-    <row r="441" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:20" ns3:dyDescent="0.2">
       <c r="A441" t="s">
         <v>28</v>
       </c>
@@ -29748,7 +29748,7 @@
         <v>35145</v>
       </c>
     </row>
-    <row r="442" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:20" ns3:dyDescent="0.2">
       <c r="A442" t="s">
         <v>20</v>
       </c>
@@ -29814,7 +29814,7 @@
         <v>2243.5</v>
       </c>
     </row>
-    <row r="443" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:20" ns3:dyDescent="0.2">
       <c r="A443" t="s">
         <v>20</v>
       </c>
@@ -29880,7 +29880,7 @@
         <v>10718.324999999997</v>
       </c>
     </row>
-    <row r="444" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:20" ns3:dyDescent="0.2">
       <c r="A444" t="s">
         <v>26</v>
       </c>
@@ -29946,7 +29946,7 @@
         <v>47787</v>
       </c>
     </row>
-    <row r="445" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:20" ns3:dyDescent="0.2">
       <c r="A445" t="s">
         <v>28</v>
       </c>
@@ -30012,7 +30012,7 @@
         <v>108381.75</v>
       </c>
     </row>
-    <row r="446" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:20" ns3:dyDescent="0.2">
       <c r="A446" t="s">
         <v>35</v>
       </c>
@@ -30078,7 +30078,7 @@
         <v>30919.68</v>
       </c>
     </row>
-    <row r="447" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:20" ns3:dyDescent="0.2">
       <c r="A447" t="s">
         <v>35</v>
       </c>
@@ -30144,7 +30144,7 @@
         <v>18627.84</v>
       </c>
     </row>
-    <row r="448" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:20" ns3:dyDescent="0.2">
       <c r="A448" t="s">
         <v>28</v>
       </c>
@@ -30210,7 +30210,7 @@
         <v>66960</v>
       </c>
     </row>
-    <row r="449" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:20" ns3:dyDescent="0.2">
       <c r="A449" t="s">
         <v>20</v>
       </c>
@@ -30276,7 +30276,7 @@
         <v>12398.400000000001</v>
       </c>
     </row>
-    <row r="450" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:20" ns3:dyDescent="0.2">
       <c r="A450" t="s">
         <v>28</v>
       </c>
@@ -30342,7 +30342,7 @@
         <v>3968.9399999999987</v>
       </c>
     </row>
-    <row r="451" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:20" ns3:dyDescent="0.2">
       <c r="A451" t="s">
         <v>28</v>
       </c>
@@ -30408,7 +30408,7 @@
         <v>16687</v>
       </c>
     </row>
-    <row r="452" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:20" ns3:dyDescent="0.2">
       <c r="A452" t="s">
         <v>35</v>
       </c>
@@ -30474,7 +30474,7 @@
         <v>4248.24</v>
       </c>
     </row>
-    <row r="453" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:20" ns3:dyDescent="0.2">
       <c r="A453" t="s">
         <v>26</v>
       </c>
@@ -30540,7 +30540,7 @@
         <v>6408</v>
       </c>
     </row>
-    <row r="454" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:20" ns3:dyDescent="0.2">
       <c r="A454" t="s">
         <v>26</v>
       </c>
@@ -30606,7 +30606,7 @@
         <v>19680</v>
       </c>
     </row>
-    <row r="455" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:20" ns3:dyDescent="0.2">
       <c r="A455" t="s">
         <v>28</v>
       </c>
@@ -30672,7 +30672,7 @@
         <v>6058.5</v>
       </c>
     </row>
-    <row r="456" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:20" ns3:dyDescent="0.2">
       <c r="A456" t="s">
         <v>20</v>
       </c>
@@ -30738,7 +30738,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="457" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:20" ns3:dyDescent="0.2">
       <c r="A457" t="s">
         <v>26</v>
       </c>
@@ -30804,7 +30804,7 @@
         <v>47900</v>
       </c>
     </row>
-    <row r="458" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:20" ns3:dyDescent="0.2">
       <c r="A458" t="s">
         <v>28</v>
       </c>
@@ -30870,7 +30870,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="459" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:20" ns3:dyDescent="0.2">
       <c r="A459" t="s">
         <v>30</v>
       </c>
@@ -30936,7 +30936,7 @@
         <v>14105</v>
       </c>
     </row>
-    <row r="460" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:20" ns3:dyDescent="0.2">
       <c r="A460" t="s">
         <v>35</v>
       </c>
@@ -31002,7 +31002,7 @@
         <v>19269</v>
       </c>
     </row>
-    <row r="461" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:20" ns3:dyDescent="0.2">
       <c r="A461" t="s">
         <v>28</v>
       </c>
@@ -31068,7 +31068,7 @@
         <v>3531.8999999999996</v>
       </c>
     </row>
-    <row r="462" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:20" ns3:dyDescent="0.2">
       <c r="A462" t="s">
         <v>30</v>
       </c>
@@ -31134,7 +31134,7 @@
         <v>3461.25</v>
       </c>
     </row>
-    <row r="463" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:20" ns3:dyDescent="0.2">
       <c r="A463" t="s">
         <v>26</v>
       </c>
@@ -31200,7 +31200,7 @@
         <v>76834</v>
       </c>
     </row>
-    <row r="464" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:20" ns3:dyDescent="0.2">
       <c r="A464" t="s">
         <v>28</v>
       </c>
@@ -31266,7 +31266,7 @@
         <v>130539</v>
       </c>
     </row>
-    <row r="465" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:20" ns3:dyDescent="0.2">
       <c r="A465" t="s">
         <v>26</v>
       </c>
@@ -31332,7 +31332,7 @@
         <v>70642</v>
       </c>
     </row>
-    <row r="466" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:20" ns3:dyDescent="0.2">
       <c r="A466" t="s">
         <v>35</v>
       </c>
@@ -31398,7 +31398,7 @@
         <v>9433.2000000000007</v>
       </c>
     </row>
-    <row r="467" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:20" ns3:dyDescent="0.2">
       <c r="A467" t="s">
         <v>28</v>
       </c>
@@ -31464,7 +31464,7 @@
         <v>25488</v>
       </c>
     </row>
-    <row r="468" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:20" ns3:dyDescent="0.2">
       <c r="A468" t="s">
         <v>28</v>
       </c>
@@ -31530,7 +31530,7 @@
         <v>14211</v>
       </c>
     </row>
-    <row r="469" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:20" ns3:dyDescent="0.2">
       <c r="A469" t="s">
         <v>28</v>
       </c>
@@ -31596,7 +31596,7 @@
         <v>40020</v>
       </c>
     </row>
-    <row r="470" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:20" ns3:dyDescent="0.2">
       <c r="A470" t="s">
         <v>20</v>
       </c>
@@ -31662,7 +31662,7 @@
         <v>9011.7999999999993</v>
       </c>
     </row>
-    <row r="471" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:20" ns3:dyDescent="0.2">
       <c r="A471" t="s">
         <v>20</v>
       </c>
@@ -31728,7 +31728,7 @@
         <v>7146.2999999999993</v>
       </c>
     </row>
-    <row r="472" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:20" ns3:dyDescent="0.2">
       <c r="A472" t="s">
         <v>28</v>
       </c>
@@ -31794,7 +31794,7 @@
         <v>8808.7999999999993</v>
       </c>
     </row>
-    <row r="473" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:20" ns3:dyDescent="0.2">
       <c r="A473" t="s">
         <v>35</v>
       </c>
@@ -31860,7 +31860,7 @@
         <v>15373.439999999999</v>
       </c>
     </row>
-    <row r="474" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:20" ns3:dyDescent="0.2">
       <c r="A474" t="s">
         <v>20</v>
       </c>
@@ -31926,7 +31926,7 @@
         <v>8298.9500000000007</v>
       </c>
     </row>
-    <row r="475" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:20" ns3:dyDescent="0.2">
       <c r="A475" t="s">
         <v>28</v>
       </c>
@@ -31992,7 +31992,7 @@
         <v>5237.3999999999996</v>
       </c>
     </row>
-    <row r="476" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:20" ns3:dyDescent="0.2">
       <c r="A476" t="s">
         <v>30</v>
       </c>
@@ -32058,7 +32058,7 @@
         <v>-7700</v>
       </c>
     </row>
-    <row r="477" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:20" ns3:dyDescent="0.2">
       <c r="A477" t="s">
         <v>26</v>
       </c>
@@ -32124,7 +32124,7 @@
         <v>40612</v>
       </c>
     </row>
-    <row r="478" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:20" ns3:dyDescent="0.2">
       <c r="A478" t="s">
         <v>28</v>
       </c>
@@ -32190,7 +32190,7 @@
         <v>976.31999999999971</v>
       </c>
     </row>
-    <row r="479" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:20" ns3:dyDescent="0.2">
       <c r="A479" t="s">
         <v>28</v>
       </c>
@@ -32256,7 +32256,7 @@
         <v>2301.1200000000008</v>
       </c>
     </row>
-    <row r="480" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:20" ns3:dyDescent="0.2">
       <c r="A480" t="s">
         <v>28</v>
       </c>
@@ -32322,7 +32322,7 @@
         <v>23622</v>
       </c>
     </row>
-    <row r="481" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:20" ns3:dyDescent="0.2">
       <c r="A481" t="s">
         <v>28</v>
       </c>
@@ -32388,7 +32388,7 @@
         <v>26164</v>
       </c>
     </row>
-    <row r="482" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:20" ns3:dyDescent="0.2">
       <c r="A482" t="s">
         <v>28</v>
       </c>
@@ -32454,7 +32454,7 @@
         <v>154385</v>
       </c>
     </row>
-    <row r="483" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:20" ns3:dyDescent="0.2">
       <c r="A483" t="s">
         <v>35</v>
       </c>
@@ -32520,7 +32520,7 @@
         <v>20077.2</v>
       </c>
     </row>
-    <row r="484" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:20" ns3:dyDescent="0.2">
       <c r="A484" t="s">
         <v>28</v>
       </c>
@@ -32586,7 +32586,7 @@
         <v>18673.199999999997</v>
       </c>
     </row>
-    <row r="485" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:20" ns3:dyDescent="0.2">
       <c r="A485" t="s">
         <v>20</v>
       </c>
@@ -32652,7 +32652,7 @@
         <v>6646.4000000000015</v>
       </c>
     </row>
-    <row r="486" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:20" ns3:dyDescent="0.2">
       <c r="A486" t="s">
         <v>28</v>
       </c>
@@ -32718,7 +32718,7 @@
         <v>2938.6399999999994</v>
       </c>
     </row>
-    <row r="487" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:20" ns3:dyDescent="0.2">
       <c r="A487" t="s">
         <v>26</v>
       </c>
@@ -32784,7 +32784,7 @@
         <v>20328</v>
       </c>
     </row>
-    <row r="488" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:20" ns3:dyDescent="0.2">
       <c r="A488" t="s">
         <v>35</v>
       </c>
@@ -32850,7 +32850,7 @@
         <v>18117</v>
       </c>
     </row>
-    <row r="489" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:20" ns3:dyDescent="0.2">
       <c r="A489" t="s">
         <v>30</v>
       </c>
@@ -32916,7 +32916,7 @@
         <v>-16142.5</v>
       </c>
     </row>
-    <row r="490" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:20" ns3:dyDescent="0.2">
       <c r="A490" t="s">
         <v>30</v>
       </c>
@@ -32982,7 +32982,7 @@
         <v>-38046.25</v>
       </c>
     </row>
-    <row r="491" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:20" ns3:dyDescent="0.2">
       <c r="A491" t="s">
         <v>20</v>
       </c>
@@ -33048,7 +33048,7 @@
         <v>7037.25</v>
       </c>
     </row>
-    <row r="492" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:20" ns3:dyDescent="0.2">
       <c r="A492" t="s">
         <v>28</v>
       </c>
@@ -33114,7 +33114,7 @@
         <v>4292</v>
       </c>
     </row>
-    <row r="493" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:20" ns3:dyDescent="0.2">
       <c r="A493" t="s">
         <v>20</v>
       </c>
@@ -33180,7 +33180,7 @@
         <v>12360</v>
       </c>
     </row>
-    <row r="494" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:20" ns3:dyDescent="0.2">
       <c r="A494" t="s">
         <v>26</v>
       </c>
@@ -33246,7 +33246,7 @@
         <v>107550</v>
       </c>
     </row>
-    <row r="495" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:20" ns3:dyDescent="0.2">
       <c r="A495" t="s">
         <v>35</v>
       </c>
@@ -33312,7 +33312,7 @@
         <v>12831.599999999999</v>
       </c>
     </row>
-    <row r="496" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:20" ns3:dyDescent="0.2">
       <c r="A496" t="s">
         <v>35</v>
       </c>
@@ -33378,7 +33378,7 @@
         <v>23718.48</v>
       </c>
     </row>
-    <row r="497" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:20" ns3:dyDescent="0.2">
       <c r="A497" t="s">
         <v>20</v>
       </c>
@@ -33444,7 +33444,7 @@
         <v>3622.9500000000007</v>
       </c>
     </row>
-    <row r="498" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:20" ns3:dyDescent="0.2">
       <c r="A498" t="s">
         <v>26</v>
       </c>
@@ -33510,7 +33510,7 @@
         <v>46342</v>
       </c>
     </row>
-    <row r="499" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:20" ns3:dyDescent="0.2">
       <c r="A499" t="s">
         <v>35</v>
       </c>
@@ -33576,7 +33576,7 @@
         <v>16822.080000000002</v>
       </c>
     </row>
-    <row r="500" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:20" ns3:dyDescent="0.2">
       <c r="A500" t="s">
         <v>28</v>
       </c>
@@ -33642,7 +33642,7 @@
         <v>973.76000000000022</v>
       </c>
     </row>
-    <row r="501" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:20" ns3:dyDescent="0.2">
       <c r="A501" t="s">
         <v>20</v>
       </c>
@@ -33708,7 +33708,7 @@
         <v>959.19999999999982</v>
       </c>
     </row>
-    <row r="502" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:20" ns3:dyDescent="0.2">
       <c r="A502" t="s">
         <v>28</v>
       </c>
@@ -33774,7 +33774,7 @@
         <v>19080.800000000003</v>
       </c>
     </row>
-    <row r="503" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:20" ns3:dyDescent="0.2">
       <c r="A503" t="s">
         <v>28</v>
       </c>
@@ -33840,7 +33840,7 @@
         <v>9715.2000000000007</v>
       </c>
     </row>
-    <row r="504" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:20" ns3:dyDescent="0.2">
       <c r="A504" t="s">
         <v>28</v>
       </c>
@@ -33906,7 +33906,7 @@
         <v>144932</v>
       </c>
     </row>
-    <row r="505" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:20" ns3:dyDescent="0.2">
       <c r="A505" t="s">
         <v>20</v>
       </c>
@@ -33972,7 +33972,7 @@
         <v>11135</v>
       </c>
     </row>
-    <row r="506" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:20" ns3:dyDescent="0.2">
       <c r="A506" t="s">
         <v>35</v>
       </c>
@@ -34038,7 +34038,7 @@
         <v>4653.3599999999997</v>
       </c>
     </row>
-    <row r="507" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:20" ns3:dyDescent="0.2">
       <c r="A507" t="s">
         <v>28</v>
       </c>
@@ -34104,7 +34104,7 @@
         <v>115851</v>
       </c>
     </row>
-    <row r="508" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:20" ns3:dyDescent="0.2">
       <c r="A508" t="s">
         <v>28</v>
       </c>
@@ -34170,7 +34170,7 @@
         <v>13201</v>
       </c>
     </row>
-    <row r="509" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:20" ns3:dyDescent="0.2">
       <c r="A509" t="s">
         <v>30</v>
       </c>
@@ -34236,7 +34236,7 @@
         <v>-7826.25</v>
       </c>
     </row>
-    <row r="510" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:20" ns3:dyDescent="0.2">
       <c r="A510" t="s">
         <v>28</v>
       </c>
@@ -34302,7 +34302,7 @@
         <v>188378</v>
       </c>
     </row>
-    <row r="511" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:20" ns3:dyDescent="0.2">
       <c r="A511" t="s">
         <v>28</v>
       </c>
@@ -34368,7 +34368,7 @@
         <v>16245.599999999999</v>
       </c>
     </row>
-    <row r="512" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:20" ns3:dyDescent="0.2">
       <c r="A512" t="s">
         <v>28</v>
       </c>
@@ -34434,7 +34434,7 @@
         <v>25141.199999999997</v>
       </c>
     </row>
-    <row r="513" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:20" ns3:dyDescent="0.2">
       <c r="A513" t="s">
         <v>26</v>
       </c>
@@ -34500,7 +34500,7 @@
         <v>55484</v>
       </c>
     </row>
-    <row r="514" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:20" ns3:dyDescent="0.2">
       <c r="A514" t="s">
         <v>30</v>
       </c>
@@ -34566,7 +34566,7 @@
         <v>-3543.75</v>
       </c>
     </row>
-    <row r="515" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:20" ns3:dyDescent="0.2">
       <c r="A515" t="s">
         <v>30</v>
       </c>
@@ -34632,7 +34632,7 @@
         <v>-13187.5</v>
       </c>
     </row>
-    <row r="516" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:20" ns3:dyDescent="0.2">
       <c r="A516" t="s">
         <v>26</v>
       </c>
@@ -34698,7 +34698,7 @@
         <v>42941</v>
       </c>
     </row>
-    <row r="517" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:20" ns3:dyDescent="0.2">
       <c r="A517" t="s">
         <v>28</v>
       </c>
@@ -34764,7 +34764,7 @@
         <v>121153.5</v>
       </c>
     </row>
-    <row r="518" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:20" ns3:dyDescent="0.2">
       <c r="A518" t="s">
         <v>35</v>
       </c>
@@ -34830,7 +34830,7 @@
         <v>12513.599999999999</v>
       </c>
     </row>
-    <row r="519" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:20" ns3:dyDescent="0.2">
       <c r="A519" t="s">
         <v>28</v>
       </c>
@@ -34896,7 +34896,7 @@
         <v>3026.3999999999996</v>
       </c>
     </row>
-    <row r="520" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:20" ns3:dyDescent="0.2">
       <c r="A520" t="s">
         <v>30</v>
       </c>
@@ -34962,7 +34962,7 @@
         <v>-11970</v>
       </c>
     </row>
-    <row r="521" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:20" ns3:dyDescent="0.2">
       <c r="A521" t="s">
         <v>26</v>
       </c>
@@ -35028,7 +35028,7 @@
         <v>8640</v>
       </c>
     </row>
-    <row r="522" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:20" ns3:dyDescent="0.2">
       <c r="A522" t="s">
         <v>28</v>
       </c>
@@ -35094,7 +35094,7 @@
         <v>38885</v>
       </c>
     </row>
-    <row r="523" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:20" ns3:dyDescent="0.2">
       <c r="A523" t="s">
         <v>28</v>
       </c>
@@ -35160,7 +35160,7 @@
         <v>2807.2000000000007</v>
       </c>
     </row>
-    <row r="524" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:20" ns3:dyDescent="0.2">
       <c r="A524" t="s">
         <v>20</v>
       </c>
@@ -35226,7 +35226,7 @@
         <v>5124.2999999999993</v>
       </c>
     </row>
-    <row r="525" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:20" ns3:dyDescent="0.2">
       <c r="A525" t="s">
         <v>28</v>
       </c>
@@ -35292,7 +35292,7 @@
         <v>395.76000000000022</v>
       </c>
     </row>
-    <row r="526" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:20" ns3:dyDescent="0.2">
       <c r="A526" t="s">
         <v>30</v>
       </c>
@@ -35358,7 +35358,7 @@
         <v>-9116.25</v>
       </c>
     </row>
-    <row r="527" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:20" ns3:dyDescent="0.2">
       <c r="A527" t="s">
         <v>28</v>
       </c>
@@ -35424,7 +35424,7 @@
         <v>2286</v>
       </c>
     </row>
-    <row r="528" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:20" ns3:dyDescent="0.2">
       <c r="A528" t="s">
         <v>28</v>
       </c>
@@ -35490,7 +35490,7 @@
         <v>2286</v>
       </c>
     </row>
-    <row r="529" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:20" ns3:dyDescent="0.2">
       <c r="A529" t="s">
         <v>28</v>
       </c>
@@ -35556,7 +35556,7 @@
         <v>120840.5</v>
       </c>
     </row>
-    <row r="530" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:20" ns3:dyDescent="0.2">
       <c r="A530" t="s">
         <v>28</v>
       </c>
@@ -35622,7 +35622,7 @@
         <v>120840.5</v>
       </c>
     </row>
-    <row r="531" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:20" ns3:dyDescent="0.2">
       <c r="A531" t="s">
         <v>35</v>
       </c>
@@ -35688,7 +35688,7 @@
         <v>11344.2</v>
       </c>
     </row>
-    <row r="532" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:20" ns3:dyDescent="0.2">
       <c r="A532" t="s">
         <v>28</v>
       </c>
@@ -35754,7 +35754,7 @@
         <v>15033.599999999999</v>
       </c>
     </row>
-    <row r="533" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:20" ns3:dyDescent="0.2">
       <c r="A533" t="s">
         <v>35</v>
       </c>
@@ -35820,7 +35820,7 @@
         <v>11344.2</v>
       </c>
     </row>
-    <row r="534" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:20" ns3:dyDescent="0.2">
       <c r="A534" t="s">
         <v>28</v>
       </c>
@@ -35886,7 +35886,7 @@
         <v>15033.599999999999</v>
       </c>
     </row>
-    <row r="535" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:20" ns3:dyDescent="0.2">
       <c r="A535" t="s">
         <v>28</v>
       </c>
@@ -35952,7 +35952,7 @@
         <v>238791</v>
       </c>
     </row>
-    <row r="536" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:20" ns3:dyDescent="0.2">
       <c r="A536" t="s">
         <v>28</v>
       </c>
@@ -36018,7 +36018,7 @@
         <v>238791</v>
       </c>
     </row>
-    <row r="537" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:20" ns3:dyDescent="0.2">
       <c r="A537" t="s">
         <v>30</v>
       </c>
@@ -36084,7 +36084,7 @@
         <v>2511.25</v>
       </c>
     </row>
-    <row r="538" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:20" ns3:dyDescent="0.2">
       <c r="A538" t="s">
         <v>30</v>
       </c>
@@ -36150,7 +36150,7 @@
         <v>2511.25</v>
       </c>
     </row>
-    <row r="539" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:20" ns3:dyDescent="0.2">
       <c r="A539" t="s">
         <v>20</v>
       </c>
@@ -36216,7 +36216,7 @@
         <v>8936.4000000000015</v>
       </c>
     </row>
-    <row r="540" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:20" ns3:dyDescent="0.2">
       <c r="A540" t="s">
         <v>20</v>
       </c>
@@ -36282,7 +36282,7 @@
         <v>8936.4000000000015</v>
       </c>
     </row>
-    <row r="541" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:20" ns3:dyDescent="0.2">
       <c r="A541" t="s">
         <v>26</v>
       </c>
@@ -36348,7 +36348,7 @@
         <v>76798</v>
       </c>
     </row>
-    <row r="542" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:20" ns3:dyDescent="0.2">
       <c r="A542" t="s">
         <v>26</v>
       </c>
@@ -36414,7 +36414,7 @@
         <v>76798</v>
       </c>
     </row>
-    <row r="543" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:20" ns3:dyDescent="0.2">
       <c r="A543" t="s">
         <v>28</v>
       </c>
@@ -36480,7 +36480,7 @@
         <v>165452</v>
       </c>
     </row>
-    <row r="544" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:20" ns3:dyDescent="0.2">
       <c r="A544" t="s">
         <v>28</v>
       </c>
@@ -36546,7 +36546,7 @@
         <v>165452</v>
       </c>
     </row>
-    <row r="545" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:20" ns3:dyDescent="0.2">
       <c r="A545" t="s">
         <v>28</v>
       </c>
@@ -36612,7 +36612,7 @@
         <v>4436.8499999999985</v>
       </c>
     </row>
-    <row r="546" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:20" ns3:dyDescent="0.2">
       <c r="A546" t="s">
         <v>28</v>
       </c>
@@ -36678,7 +36678,7 @@
         <v>4436.8499999999985</v>
       </c>
     </row>
-    <row r="547" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:20" ns3:dyDescent="0.2">
       <c r="A547" t="s">
         <v>30</v>
       </c>
@@ -36744,7 +36744,7 @@
         <v>-1076.25</v>
       </c>
     </row>
-    <row r="548" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:20" ns3:dyDescent="0.2">
       <c r="A548" t="s">
         <v>30</v>
       </c>
@@ -36810,7 +36810,7 @@
         <v>-1076.25</v>
       </c>
     </row>
-    <row r="549" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:20" ns3:dyDescent="0.2">
       <c r="A549" t="s">
         <v>20</v>
       </c>
@@ -36876,7 +36876,7 @@
         <v>4727.2999999999993</v>
       </c>
     </row>
-    <row r="550" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:20" ns3:dyDescent="0.2">
       <c r="A550" t="s">
         <v>20</v>
       </c>
@@ -36942,7 +36942,7 @@
         <v>4727.2999999999993</v>
       </c>
     </row>
-    <row r="551" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:20" ns3:dyDescent="0.2">
       <c r="A551" t="s">
         <v>26</v>
       </c>
@@ -37008,7 +37008,7 @@
         <v>63249</v>
       </c>
     </row>
-    <row r="552" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:20" ns3:dyDescent="0.2">
       <c r="A552" t="s">
         <v>28</v>
       </c>
@@ -37074,7 +37074,7 @@
         <v>16993.599999999999</v>
       </c>
     </row>
-    <row r="553" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:20" ns3:dyDescent="0.2">
       <c r="A553" t="s">
         <v>26</v>
       </c>
@@ -37140,7 +37140,7 @@
         <v>63249</v>
       </c>
     </row>
-    <row r="554" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:20" ns3:dyDescent="0.2">
       <c r="A554" t="s">
         <v>28</v>
       </c>
@@ -37206,7 +37206,7 @@
         <v>16993.599999999999</v>
       </c>
     </row>
-    <row r="555" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:20" ns3:dyDescent="0.2">
       <c r="A555" t="s">
         <v>20</v>
       </c>
@@ -37272,7 +37272,7 @@
         <v>4478.5499999999993</v>
       </c>
     </row>
-    <row r="556" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:20" ns3:dyDescent="0.2">
       <c r="A556" t="s">
         <v>28</v>
       </c>
@@ -37338,7 +37338,7 @@
         <v>74236.5</v>
       </c>
     </row>
-    <row r="557" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:20" ns3:dyDescent="0.2">
       <c r="A557" t="s">
         <v>20</v>
       </c>
@@ -37404,7 +37404,7 @@
         <v>4478.5499999999993</v>
       </c>
     </row>
-    <row r="558" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:20" ns3:dyDescent="0.2">
       <c r="A558" t="s">
         <v>28</v>
       </c>
@@ -37470,7 +37470,7 @@
         <v>74236.5</v>
       </c>
     </row>
-    <row r="559" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:20" ns3:dyDescent="0.2">
       <c r="A559" t="s">
         <v>28</v>
       </c>
@@ -37536,7 +37536,7 @@
         <v>493.19999999999982</v>
       </c>
     </row>
-    <row r="560" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:20" ns3:dyDescent="0.2">
       <c r="A560" t="s">
         <v>28</v>
       </c>
@@ -37602,7 +37602,7 @@
         <v>493.19999999999982</v>
       </c>
     </row>
-    <row r="561" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:20" ns3:dyDescent="0.2">
       <c r="A561" t="s">
         <v>28</v>
       </c>
@@ -37668,7 +37668,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="562" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:20" ns3:dyDescent="0.2">
       <c r="A562" t="s">
         <v>28</v>
       </c>
@@ -37734,7 +37734,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="563" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:20" ns3:dyDescent="0.2">
       <c r="A563" t="s">
         <v>35</v>
       </c>
@@ -37800,7 +37800,7 @@
         <v>3624.96</v>
       </c>
     </row>
-    <row r="564" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:20" ns3:dyDescent="0.2">
       <c r="A564" t="s">
         <v>35</v>
       </c>
@@ -37866,7 +37866,7 @@
         <v>3624.96</v>
       </c>
     </row>
-    <row r="565" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:20" ns3:dyDescent="0.2">
       <c r="A565" t="s">
         <v>30</v>
       </c>
@@ -37932,7 +37932,7 @@
         <v>-21358.75</v>
       </c>
     </row>
-    <row r="566" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:20" ns3:dyDescent="0.2">
       <c r="A566" t="s">
         <v>30</v>
       </c>
@@ -37998,7 +37998,7 @@
         <v>-21358.75</v>
       </c>
     </row>
-    <row r="567" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:20" ns3:dyDescent="0.2">
       <c r="A567" t="s">
         <v>30</v>
       </c>
@@ -38064,7 +38064,7 @@
         <v>-21560</v>
       </c>
     </row>
-    <row r="568" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:20" ns3:dyDescent="0.2">
       <c r="A568" t="s">
         <v>28</v>
       </c>
@@ -38130,7 +38130,7 @@
         <v>3171.4399999999987</v>
       </c>
     </row>
-    <row r="569" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:20" ns3:dyDescent="0.2">
       <c r="A569" t="s">
         <v>30</v>
       </c>
@@ -38196,7 +38196,7 @@
         <v>-21560</v>
       </c>
     </row>
-    <row r="570" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:20" ns3:dyDescent="0.2">
       <c r="A570" t="s">
         <v>28</v>
       </c>
@@ -38262,7 +38262,7 @@
         <v>6878</v>
       </c>
     </row>
-    <row r="571" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:20" ns3:dyDescent="0.2">
       <c r="A571" t="s">
         <v>28</v>
       </c>
@@ -38328,7 +38328,7 @@
         <v>47328</v>
       </c>
     </row>
-    <row r="572" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:20" ns3:dyDescent="0.2">
       <c r="A572" t="s">
         <v>28</v>
       </c>
@@ -38394,7 +38394,7 @@
         <v>6878</v>
       </c>
     </row>
-    <row r="573" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:20" ns3:dyDescent="0.2">
       <c r="A573" t="s">
         <v>28</v>
       </c>
@@ -38460,7 +38460,7 @@
         <v>47328</v>
       </c>
     </row>
-    <row r="574" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:20" ns3:dyDescent="0.2">
       <c r="A574" t="s">
         <v>28</v>
       </c>
@@ -38526,7 +38526,7 @@
         <v>3171.4399999999987</v>
       </c>
     </row>
-    <row r="575" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:20" ns3:dyDescent="0.2">
       <c r="A575" t="s">
         <v>28</v>
       </c>
@@ -38592,7 +38592,7 @@
         <v>9242.5999999999985</v>
       </c>
     </row>
-    <row r="576" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:20" ns3:dyDescent="0.2">
       <c r="A576" t="s">
         <v>20</v>
       </c>
@@ -38658,7 +38658,7 @@
         <v>4773.25</v>
       </c>
     </row>
-    <row r="577" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:20" ns3:dyDescent="0.2">
       <c r="A577" t="s">
         <v>28</v>
       </c>
@@ -38724,7 +38724,7 @@
         <v>9242.5999999999985</v>
       </c>
     </row>
-    <row r="578" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:20" ns3:dyDescent="0.2">
       <c r="A578" t="s">
         <v>35</v>
       </c>
@@ -38790,7 +38790,7 @@
         <v>3050.3999999999996</v>
       </c>
     </row>
-    <row r="579" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:20" ns3:dyDescent="0.2">
       <c r="A579" t="s">
         <v>20</v>
       </c>
@@ -38856,7 +38856,7 @@
         <v>4773.25</v>
       </c>
     </row>
-    <row r="580" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:20" ns3:dyDescent="0.2">
       <c r="A580" t="s">
         <v>35</v>
       </c>
@@ -38922,7 +38922,7 @@
         <v>3050.3999999999996</v>
       </c>
     </row>
-    <row r="581" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:20" ns3:dyDescent="0.2">
       <c r="A581" t="s">
         <v>35</v>
       </c>
@@ -38988,7 +38988,7 @@
         <v>10196.76</v>
       </c>
     </row>
-    <row r="582" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:20" ns3:dyDescent="0.2">
       <c r="A582" t="s">
         <v>35</v>
       </c>
@@ -39054,7 +39054,7 @@
         <v>10196.76</v>
       </c>
     </row>
-    <row r="583" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:20" ns3:dyDescent="0.2">
       <c r="A583" t="s">
         <v>26</v>
       </c>
@@ -39120,7 +39120,7 @@
         <v>11968</v>
       </c>
     </row>
-    <row r="584" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:20" ns3:dyDescent="0.2">
       <c r="A584" t="s">
         <v>26</v>
       </c>
@@ -39186,7 +39186,7 @@
         <v>8080</v>
       </c>
     </row>
-    <row r="585" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:20" ns3:dyDescent="0.2">
       <c r="A585" t="s">
         <v>35</v>
       </c>
@@ -39252,7 +39252,7 @@
         <v>21330.48</v>
       </c>
     </row>
-    <row r="586" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:20" ns3:dyDescent="0.2">
       <c r="A586" t="s">
         <v>28</v>
       </c>
@@ -39318,7 +39318,7 @@
         <v>1765.619999999999</v>
       </c>
     </row>
-    <row r="587" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:20" ns3:dyDescent="0.2">
       <c r="A587" t="s">
         <v>26</v>
       </c>
@@ -39384,7 +39384,7 @@
         <v>11968</v>
       </c>
     </row>
-    <row r="588" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:20" ns3:dyDescent="0.2">
       <c r="A588" t="s">
         <v>26</v>
       </c>
@@ -39450,7 +39450,7 @@
         <v>8080</v>
       </c>
     </row>
-    <row r="589" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:20" ns3:dyDescent="0.2">
       <c r="A589" t="s">
         <v>35</v>
       </c>
@@ -39516,7 +39516,7 @@
         <v>21330.48</v>
       </c>
     </row>
-    <row r="590" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:20" ns3:dyDescent="0.2">
       <c r="A590" t="s">
         <v>28</v>
       </c>
@@ -39582,7 +39582,7 @@
         <v>1765.619999999999</v>
       </c>
     </row>
-    <row r="591" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:20" ns3:dyDescent="0.2">
       <c r="A591" t="s">
         <v>30</v>
       </c>
@@ -39648,7 +39648,7 @@
         <v>-14918.75</v>
       </c>
     </row>
-    <row r="592" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:20" ns3:dyDescent="0.2">
       <c r="A592" t="s">
         <v>26</v>
       </c>
@@ -39714,7 +39714,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="593" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:20" ns3:dyDescent="0.2">
       <c r="A593" t="s">
         <v>30</v>
       </c>
@@ -39780,7 +39780,7 @@
         <v>-14918.75</v>
       </c>
     </row>
-    <row r="594" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:20" ns3:dyDescent="0.2">
       <c r="A594" t="s">
         <v>20</v>
       </c>
@@ -39846,7 +39846,7 @@
         <v>3231.25</v>
       </c>
     </row>
-    <row r="595" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:20" ns3:dyDescent="0.2">
       <c r="A595" t="s">
         <v>20</v>
       </c>
@@ -39912,7 +39912,7 @@
         <v>3231.25</v>
       </c>
     </row>
-    <row r="596" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:20" ns3:dyDescent="0.2">
       <c r="A596" t="s">
         <v>26</v>
       </c>
@@ -39978,7 +39978,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="597" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:20" ns3:dyDescent="0.2">
       <c r="A597" t="s">
         <v>28</v>
       </c>
@@ -40044,7 +40044,7 @@
         <v>1233.2700000000004</v>
       </c>
     </row>
-    <row r="598" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:20" ns3:dyDescent="0.2">
       <c r="A598" t="s">
         <v>26</v>
       </c>
@@ -40110,7 +40110,7 @@
         <v>136535</v>
       </c>
     </row>
-    <row r="599" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:20" ns3:dyDescent="0.2">
       <c r="A599" t="s">
         <v>30</v>
       </c>
@@ -40176,7 +40176,7 @@
         <v>6540</v>
       </c>
     </row>
-    <row r="600" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:20" ns3:dyDescent="0.2">
       <c r="A600" t="s">
         <v>35</v>
       </c>
@@ -40242,7 +40242,7 @@
         <v>6044.4</v>
       </c>
     </row>
-    <row r="601" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:20" ns3:dyDescent="0.2">
       <c r="A601" t="s">
         <v>28</v>
       </c>
@@ -40308,7 +40308,7 @@
         <v>11865.599999999999</v>
       </c>
     </row>
-    <row r="602" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:20" ns3:dyDescent="0.2">
       <c r="A602" t="s">
         <v>28</v>
       </c>
@@ -40374,7 +40374,7 @@
         <v>9033.5999999999985</v>
       </c>
     </row>
-    <row r="603" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:20" ns3:dyDescent="0.2">
       <c r="A603" t="s">
         <v>20</v>
       </c>
@@ -40440,7 +40440,7 @@
         <v>11861.75</v>
       </c>
     </row>
-    <row r="604" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:20" ns3:dyDescent="0.2">
       <c r="A604" t="s">
         <v>35</v>
       </c>
@@ -40506,7 +40506,7 @@
         <v>19672.8</v>
       </c>
     </row>
-    <row r="605" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:20" ns3:dyDescent="0.2">
       <c r="A605" t="s">
         <v>20</v>
       </c>
@@ -40572,7 +40572,7 @@
         <v>8323</v>
       </c>
     </row>
-    <row r="606" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:20" ns3:dyDescent="0.2">
       <c r="A606" t="s">
         <v>35</v>
       </c>
@@ -40638,7 +40638,7 @@
         <v>22546.44</v>
       </c>
     </row>
-    <row r="607" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:20" ns3:dyDescent="0.2">
       <c r="A607" t="s">
         <v>28</v>
       </c>
@@ -40704,7 +40704,7 @@
         <v>2106.1399999999994</v>
       </c>
     </row>
-    <row r="608" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:20" ns3:dyDescent="0.2">
       <c r="A608" t="s">
         <v>35</v>
       </c>
@@ -40770,7 +40770,7 @@
         <v>19110.72</v>
       </c>
     </row>
-    <row r="609" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:20" ns3:dyDescent="0.2">
       <c r="A609" t="s">
         <v>28</v>
       </c>
@@ -40836,7 +40836,7 @@
         <v>825.97000000000025</v>
       </c>
     </row>
-    <row r="610" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:20" ns3:dyDescent="0.2">
       <c r="A610" t="s">
         <v>28</v>
       </c>
@@ -40902,7 +40902,7 @@
         <v>9614.7999999999993</v>
       </c>
     </row>
-    <row r="611" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:20" ns3:dyDescent="0.2">
       <c r="A611" t="s">
         <v>20</v>
       </c>
@@ -40968,7 +40968,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="612" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:20" ns3:dyDescent="0.2">
       <c r="A612" t="s">
         <v>28</v>
       </c>
@@ -41034,7 +41034,7 @@
         <v>12768</v>
       </c>
     </row>
-    <row r="613" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:20" ns3:dyDescent="0.2">
       <c r="A613" t="s">
         <v>35</v>
       </c>
@@ -41100,7 +41100,7 @@
         <v>18382.32</v>
       </c>
     </row>
-    <row r="614" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:20" ns3:dyDescent="0.2">
       <c r="A614" t="s">
         <v>26</v>
       </c>
@@ -41166,7 +41166,7 @@
         <v>30452</v>
       </c>
     </row>
-    <row r="615" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:20" ns3:dyDescent="0.2">
       <c r="A615" t="s">
         <v>30</v>
       </c>
@@ -41232,7 +41232,7 @@
         <v>-5481.25</v>
       </c>
     </row>
-    <row r="616" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:20" ns3:dyDescent="0.2">
       <c r="A616" t="s">
         <v>28</v>
       </c>
@@ -41298,7 +41298,7 @@
         <v>13890.8</v>
       </c>
     </row>
-    <row r="617" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:20" ns3:dyDescent="0.2">
       <c r="A617" t="s">
         <v>28</v>
       </c>
@@ -41364,7 +41364,7 @@
         <v>3464.5</v>
       </c>
     </row>
-    <row r="618" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:20" ns3:dyDescent="0.2">
       <c r="A618" t="s">
         <v>30</v>
       </c>
@@ -41430,7 +41430,7 @@
         <v>-18967.5</v>
       </c>
     </row>
-    <row r="619" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:20" ns3:dyDescent="0.2">
       <c r="A619" t="s">
         <v>26</v>
       </c>
@@ -41496,7 +41496,7 @@
         <v>23222</v>
       </c>
     </row>
-    <row r="620" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:20" ns3:dyDescent="0.2">
       <c r="A620" t="s">
         <v>28</v>
       </c>
@@ -41562,7 +41562,7 @@
         <v>2223.84</v>
       </c>
     </row>
-    <row r="621" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:20" ns3:dyDescent="0.2">
       <c r="A621" t="s">
         <v>20</v>
       </c>
@@ -41628,7 +41628,7 @@
         <v>8604.8000000000029</v>
       </c>
     </row>
-    <row r="622" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:20" ns3:dyDescent="0.2">
       <c r="A622" t="s">
         <v>28</v>
       </c>
@@ -41694,7 +41694,7 @@
         <v>76512</v>
       </c>
     </row>
-    <row r="623" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:20" ns3:dyDescent="0.2">
       <c r="A623" t="s">
         <v>26</v>
       </c>
@@ -41760,7 +41760,7 @@
         <v>19026</v>
       </c>
     </row>
-    <row r="624" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:20" ns3:dyDescent="0.2">
       <c r="A624" t="s">
         <v>26</v>
       </c>
@@ -41826,7 +41826,7 @@
         <v>30100</v>
       </c>
     </row>
-    <row r="625" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:20" ns3:dyDescent="0.2">
       <c r="A625" t="s">
         <v>28</v>
       </c>
@@ -41892,7 +41892,7 @@
         <v>57456</v>
       </c>
     </row>
-    <row r="626" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:20" ns3:dyDescent="0.2">
       <c r="A626" t="s">
         <v>30</v>
       </c>
@@ -41958,7 +41958,7 @@
         <v>-23870</v>
       </c>
     </row>
-    <row r="627" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:20" ns3:dyDescent="0.2">
       <c r="A627" t="s">
         <v>28</v>
       </c>
@@ -42024,7 +42024,7 @@
         <v>15886.5</v>
       </c>
     </row>
-    <row r="628" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:20" ns3:dyDescent="0.2">
       <c r="A628" t="s">
         <v>20</v>
       </c>
@@ -42090,7 +42090,7 @@
         <v>4387.7000000000007</v>
       </c>
     </row>
-    <row r="629" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:20" ns3:dyDescent="0.2">
       <c r="A629" t="s">
         <v>28</v>
       </c>
@@ -42156,7 +42156,7 @@
         <v>28700</v>
       </c>
     </row>
-    <row r="630" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:20" ns3:dyDescent="0.2">
       <c r="A630" t="s">
         <v>28</v>
       </c>
@@ -42222,7 +42222,7 @@
         <v>48257</v>
       </c>
     </row>
-    <row r="631" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:20" ns3:dyDescent="0.2">
       <c r="A631" t="s">
         <v>30</v>
       </c>
@@ -42288,7 +42288,7 @@
         <v>-7590</v>
       </c>
     </row>
-    <row r="632" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:20" ns3:dyDescent="0.2">
       <c r="A632" t="s">
         <v>28</v>
       </c>
@@ -42354,7 +42354,7 @@
         <v>136170</v>
       </c>
     </row>
-    <row r="633" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:20" ns3:dyDescent="0.2">
       <c r="A633" t="s">
         <v>20</v>
       </c>
@@ -42420,7 +42420,7 @@
         <v>3075</v>
       </c>
     </row>
-    <row r="634" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:20" ns3:dyDescent="0.2">
       <c r="A634" t="s">
         <v>28</v>
       </c>
@@ -42486,7 +42486,7 @@
         <v>18170</v>
       </c>
     </row>
-    <row r="635" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:20" ns3:dyDescent="0.2">
       <c r="A635" t="s">
         <v>28</v>
       </c>
@@ -42552,7 +42552,7 @@
         <v>136170</v>
       </c>
     </row>
-    <row r="636" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:20" ns3:dyDescent="0.2">
       <c r="A636" t="s">
         <v>28</v>
       </c>
@@ -42618,7 +42618,7 @@
         <v>18170</v>
       </c>
     </row>
-    <row r="637" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:20" ns3:dyDescent="0.2">
       <c r="A637" t="s">
         <v>20</v>
       </c>
@@ -42684,7 +42684,7 @@
         <v>3075</v>
       </c>
     </row>
-    <row r="638" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:20" ns3:dyDescent="0.2">
       <c r="A638" t="s">
         <v>28</v>
       </c>
@@ -42750,7 +42750,7 @@
         <v>186407.5</v>
       </c>
     </row>
-    <row r="639" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:20" ns3:dyDescent="0.2">
       <c r="A639" t="s">
         <v>28</v>
       </c>
@@ -42816,7 +42816,7 @@
         <v>186407.5</v>
       </c>
     </row>
-    <row r="640" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:20" ns3:dyDescent="0.2">
       <c r="A640" t="s">
         <v>28</v>
       </c>
@@ -42882,7 +42882,7 @@
         <v>236716</v>
       </c>
     </row>
-    <row r="641" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:20" ns3:dyDescent="0.2">
       <c r="A641" t="s">
         <v>26</v>
       </c>
@@ -42948,7 +42948,7 @@
         <v>84304</v>
       </c>
     </row>
-    <row r="642" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:20" ns3:dyDescent="0.2">
       <c r="A642" t="s">
         <v>28</v>
       </c>
@@ -43014,7 +43014,7 @@
         <v>236716</v>
       </c>
     </row>
-    <row r="643" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:20" ns3:dyDescent="0.2">
       <c r="A643" t="s">
         <v>30</v>
       </c>
@@ -43080,7 +43080,7 @@
         <v>6822.5</v>
       </c>
     </row>
-    <row r="644" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:20" ns3:dyDescent="0.2">
       <c r="A644" t="s">
         <v>35</v>
       </c>
@@ -43146,7 +43146,7 @@
         <v>9241.7999999999993</v>
       </c>
     </row>
-    <row r="645" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:20" ns3:dyDescent="0.2">
       <c r="A645" t="s">
         <v>35</v>
       </c>
@@ -43212,7 +43212,7 @@
         <v>9495.84</v>
       </c>
     </row>
-    <row r="646" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:20" ns3:dyDescent="0.2">
       <c r="A646" t="s">
         <v>35</v>
       </c>
@@ -43278,7 +43278,7 @@
         <v>9241.7999999999993</v>
       </c>
     </row>
-    <row r="647" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:20" ns3:dyDescent="0.2">
       <c r="A647" t="s">
         <v>35</v>
       </c>
@@ -43344,7 +43344,7 @@
         <v>9495.84</v>
       </c>
     </row>
-    <row r="648" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:20" ns3:dyDescent="0.2">
       <c r="A648" t="s">
         <v>30</v>
       </c>
@@ -43410,7 +43410,7 @@
         <v>6822.5</v>
       </c>
     </row>
-    <row r="649" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:20" ns3:dyDescent="0.2">
       <c r="A649" t="s">
         <v>26</v>
       </c>
@@ -43476,7 +43476,7 @@
         <v>84304</v>
       </c>
     </row>
-    <row r="650" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:20" ns3:dyDescent="0.2">
       <c r="A650" t="s">
         <v>30</v>
       </c>
@@ -43542,7 +43542,7 @@
         <v>1608.75</v>
       </c>
     </row>
-    <row r="651" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:20" ns3:dyDescent="0.2">
       <c r="A651" t="s">
         <v>30</v>
       </c>
@@ -43608,7 +43608,7 @@
         <v>2132.5</v>
       </c>
     </row>
-    <row r="652" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:20" ns3:dyDescent="0.2">
       <c r="A652" t="s">
         <v>30</v>
       </c>
@@ -43674,7 +43674,7 @@
         <v>1608.75</v>
       </c>
     </row>
-    <row r="653" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:20" ns3:dyDescent="0.2">
       <c r="A653" t="s">
         <v>30</v>
       </c>
@@ -43740,7 +43740,7 @@
         <v>2132.5</v>
       </c>
     </row>
-    <row r="654" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:20" ns3:dyDescent="0.2">
       <c r="A654" t="s">
         <v>28</v>
       </c>
@@ -43806,7 +43806,7 @@
         <v>20824</v>
       </c>
     </row>
-    <row r="655" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:20" ns3:dyDescent="0.2">
       <c r="A655" t="s">
         <v>30</v>
       </c>
@@ -43872,7 +43872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="656" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:20" ns3:dyDescent="0.2">
       <c r="A656" t="s">
         <v>28</v>
       </c>
@@ -43938,7 +43938,7 @@
         <v>20824</v>
       </c>
     </row>
-    <row r="657" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:20" ns3:dyDescent="0.2">
       <c r="A657" t="s">
         <v>30</v>
       </c>
@@ -44004,7 +44004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="658" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:20" ns3:dyDescent="0.2">
       <c r="A658" t="s">
         <v>35</v>
       </c>
@@ -44070,7 +44070,7 @@
         <v>20420.400000000001</v>
       </c>
     </row>
-    <row r="659" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:20" ns3:dyDescent="0.2">
       <c r="A659" t="s">
         <v>35</v>
       </c>
@@ -44136,7 +44136,7 @@
         <v>20420.400000000001</v>
       </c>
     </row>
-    <row r="660" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:20" ns3:dyDescent="0.2">
       <c r="A660" t="s">
         <v>28</v>
       </c>
@@ -44202,7 +44202,7 @@
         <v>940.5</v>
       </c>
     </row>
-    <row r="661" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:20" ns3:dyDescent="0.2">
       <c r="A661" t="s">
         <v>28</v>
       </c>
@@ -44268,7 +44268,7 @@
         <v>4103.5499999999993</v>
       </c>
     </row>
-    <row r="662" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:20" ns3:dyDescent="0.2">
       <c r="A662" t="s">
         <v>28</v>
       </c>
@@ -44334,7 +44334,7 @@
         <v>23967</v>
       </c>
     </row>
-    <row r="663" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:20" ns3:dyDescent="0.2">
       <c r="A663" t="s">
         <v>26</v>
       </c>
@@ -44400,7 +44400,7 @@
         <v>43750</v>
       </c>
     </row>
-    <row r="664" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:20" ns3:dyDescent="0.2">
       <c r="A664" t="s">
         <v>28</v>
       </c>
@@ -44466,7 +44466,7 @@
         <v>23967</v>
       </c>
     </row>
-    <row r="665" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:20" ns3:dyDescent="0.2">
       <c r="A665" t="s">
         <v>28</v>
       </c>
@@ -44532,7 +44532,7 @@
         <v>940.5</v>
       </c>
     </row>
-    <row r="666" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:20" ns3:dyDescent="0.2">
       <c r="A666" t="s">
         <v>28</v>
       </c>
@@ -44598,7 +44598,7 @@
         <v>4103.5499999999993</v>
       </c>
     </row>
-    <row r="667" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:20" ns3:dyDescent="0.2">
       <c r="A667" t="s">
         <v>26</v>
       </c>
@@ -44664,7 +44664,7 @@
         <v>43750</v>
       </c>
     </row>
-    <row r="668" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:20" ns3:dyDescent="0.2">
       <c r="A668" t="s">
         <v>28</v>
       </c>
@@ -44730,7 +44730,7 @@
         <v>2388.8199999999997</v>
       </c>
     </row>
-    <row r="669" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:20" ns3:dyDescent="0.2">
       <c r="A669" t="s">
         <v>28</v>
       </c>
@@ -44796,7 +44796,7 @@
         <v>2388.8199999999997</v>
       </c>
     </row>
-    <row r="670" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:20" ns3:dyDescent="0.2">
       <c r="A670" t="s">
         <v>26</v>
       </c>
@@ -44862,7 +44862,7 @@
         <v>39788</v>
       </c>
     </row>
-    <row r="671" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:20" ns3:dyDescent="0.2">
       <c r="A671" t="s">
         <v>26</v>
       </c>
@@ -44928,7 +44928,7 @@
         <v>39788</v>
       </c>
     </row>
-    <row r="672" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:20" ns3:dyDescent="0.2">
       <c r="A672" t="s">
         <v>28</v>
       </c>
@@ -44994,7 +44994,7 @@
         <v>84444</v>
       </c>
     </row>
-    <row r="673" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:20" ns3:dyDescent="0.2">
       <c r="A673" t="s">
         <v>20</v>
       </c>
@@ -45060,7 +45060,7 @@
         <v>2701.7999999999993</v>
       </c>
     </row>
-    <row r="674" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:20" ns3:dyDescent="0.2">
       <c r="A674" t="s">
         <v>28</v>
       </c>
@@ -45126,7 +45126,7 @@
         <v>84444</v>
       </c>
     </row>
-    <row r="675" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:20" ns3:dyDescent="0.2">
       <c r="A675" t="s">
         <v>26</v>
       </c>
@@ -45192,7 +45192,7 @@
         <v>16510</v>
       </c>
     </row>
-    <row r="676" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:20" ns3:dyDescent="0.2">
       <c r="A676" t="s">
         <v>20</v>
       </c>
@@ -45258,7 +45258,7 @@
         <v>2701.7999999999993</v>
       </c>
     </row>
-    <row r="677" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:20" ns3:dyDescent="0.2">
       <c r="A677" t="s">
         <v>26</v>
       </c>
@@ -45324,7 +45324,7 @@
         <v>16510</v>
       </c>
     </row>
-    <row r="678" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:20" ns3:dyDescent="0.2">
       <c r="A678" t="s">
         <v>30</v>
       </c>
@@ -45390,7 +45390,7 @@
         <v>-17481.25</v>
       </c>
     </row>
-    <row r="679" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:20" ns3:dyDescent="0.2">
       <c r="A679" t="s">
         <v>30</v>
       </c>
@@ -45456,7 +45456,7 @@
         <v>-17481.25</v>
       </c>
     </row>
-    <row r="680" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:20" ns3:dyDescent="0.2">
       <c r="A680" t="s">
         <v>28</v>
       </c>
@@ -45522,7 +45522,7 @@
         <v>713.77</v>
       </c>
     </row>
-    <row r="681" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:20" ns3:dyDescent="0.2">
       <c r="A681" t="s">
         <v>28</v>
       </c>
@@ -45588,7 +45588,7 @@
         <v>713.77</v>
       </c>
     </row>
-    <row r="682" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:20" ns3:dyDescent="0.2">
       <c r="A682" t="s">
         <v>20</v>
       </c>
@@ -45654,7 +45654,7 @@
         <v>7252</v>
       </c>
     </row>
-    <row r="683" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:20" ns3:dyDescent="0.2">
       <c r="A683" t="s">
         <v>26</v>
       </c>
@@ -45720,7 +45720,7 @@
         <v>17060</v>
       </c>
     </row>
-    <row r="684" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:20" ns3:dyDescent="0.2">
       <c r="A684" t="s">
         <v>20</v>
       </c>
@@ -45786,7 +45786,7 @@
         <v>7252</v>
       </c>
     </row>
-    <row r="685" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:20" ns3:dyDescent="0.2">
       <c r="A685" t="s">
         <v>26</v>
       </c>
@@ -45852,7 +45852,7 @@
         <v>17060</v>
       </c>
     </row>
-    <row r="686" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:20" ns3:dyDescent="0.2">
       <c r="A686" t="s">
         <v>20</v>
       </c>
@@ -45918,7 +45918,7 @@
         <v>7225.9500000000007</v>
       </c>
     </row>
-    <row r="687" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:20" ns3:dyDescent="0.2">
       <c r="A687" t="s">
         <v>20</v>
       </c>
@@ -45984,7 +45984,7 @@
         <v>7225.9500000000007</v>
       </c>
     </row>
-    <row r="688" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:20" ns3:dyDescent="0.2">
       <c r="A688" t="s">
         <v>28</v>
       </c>
@@ -46050,7 +46050,7 @@
         <v>9370.7999999999993</v>
       </c>
     </row>
-    <row r="689" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:20" ns3:dyDescent="0.2">
       <c r="A689" t="s">
         <v>28</v>
       </c>
@@ -46116,7 +46116,7 @@
         <v>9370.7999999999993</v>
       </c>
     </row>
-    <row r="690" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:20" ns3:dyDescent="0.2">
       <c r="A690" t="s">
         <v>28</v>
       </c>
@@ -46182,7 +46182,7 @@
         <v>11635.599999999999</v>
       </c>
     </row>
-    <row r="691" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:20" ns3:dyDescent="0.2">
       <c r="A691" t="s">
         <v>28</v>
       </c>
@@ -46248,7 +46248,7 @@
         <v>11635.599999999999</v>
       </c>
     </row>
-    <row r="692" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:20" ns3:dyDescent="0.2">
       <c r="A692" t="s">
         <v>35</v>
       </c>
@@ -46314,7 +46314,7 @@
         <v>7536.7199999999993</v>
       </c>
     </row>
-    <row r="693" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:20" ns3:dyDescent="0.2">
       <c r="A693" t="s">
         <v>35</v>
       </c>
@@ -46380,7 +46380,7 @@
         <v>7536.7199999999993</v>
       </c>
     </row>
-    <row r="694" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:20" ns3:dyDescent="0.2">
       <c r="A694" t="s">
         <v>28</v>
       </c>
@@ -46446,7 +46446,7 @@
         <v>285.59999999999991</v>
       </c>
     </row>
-    <row r="695" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:20" ns3:dyDescent="0.2">
       <c r="A695" t="s">
         <v>28</v>
       </c>
@@ -46512,7 +46512,7 @@
         <v>285.59999999999991</v>
       </c>
     </row>
-    <row r="696" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:20" ns3:dyDescent="0.2">
       <c r="A696" t="s">
         <v>20</v>
       </c>
@@ -46578,7 +46578,7 @@
         <v>6670</v>
       </c>
     </row>
-    <row r="697" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:20" ns3:dyDescent="0.2">
       <c r="A697" t="s">
         <v>20</v>
       </c>
@@ -46644,7 +46644,7 @@
         <v>6670</v>
       </c>
     </row>
-    <row r="698" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:20" ns3:dyDescent="0.2">
       <c r="A698" t="s">
         <v>35</v>
       </c>
@@ -46710,7 +46710,7 @@
         <v>6580.7999999999993</v>
       </c>
     </row>
-    <row r="699" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:20" ns3:dyDescent="0.2">
       <c r="A699" t="s">
         <v>28</v>
       </c>
@@ -46776,7 +46776,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="700" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:20" ns3:dyDescent="0.2">
       <c r="A700" t="s">
         <v>35</v>
       </c>
@@ -46842,7 +46842,7 @@
         <v>6580.7999999999993</v>
       </c>
     </row>
-    <row r="701" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:20" ns3:dyDescent="0.2">
       <c r="A701" t="s">
         <v>28</v>
       </c>
@@ -46908,7 +46908,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="702" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:20" ht="21" customHeight="1" ns3:dyDescent="0.2">
       <c r="A702" s="9" t="s">
         <v>54</v>
       </c>
@@ -46954,10 +46954,7 @@
         <v>5530</v>
       </c>
       <c r="P702" s="9"/>
-      <c r="Q702" s="10">
-        <f>SUM(Q2:Q701)</f>
-        <v>0</v>
-      </c>
+      <c r="Q702" s="10"/>
       <c r="R702" s="11">
         <f>SUM(R2:R701)</f>
         <v>127931598.5</v>
@@ -46971,7 +46968,7 @@
         <v>16893702.260000005</v>
       </c>
     </row>
-    <row r="704" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:20" ns3:dyDescent="0.2">
       <c r="A704" s="12" t="s">
         <v>55</v>
       </c>
@@ -46980,7 +46977,7 @@
         <v>118.42857142857143</v>
       </c>
     </row>
-    <row r="705" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:2" ns3:dyDescent="0.2">
       <c r="A705" s="12" t="s">
         <v>56</v>
       </c>
@@ -46989,7 +46986,7 @@
         <v>262200</v>
       </c>
     </row>
-    <row r="706" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:2" ns3:dyDescent="0.2">
       <c r="A706" s="12" t="s">
         <v>57</v>
       </c>
